--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19A5A2C7-0112-4BF6-9F20-DDB60D1ADFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{764ECBDF-7D7D-4A43-A1A8-7B48F658F6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4758F6AE-ECFF-49F1-9EA7-9E5B1F65468A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{48D7D643-5868-48BC-BF38-53AD3B19D4F6}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
     <sheet name="CHORE CFS" sheetId="7" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CHORE CY'!$A$1:$M$40</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
   <si>
     <t>GATE IN / GATE OUT REQUEST</t>
   </si>
@@ -170,17 +173,19 @@
       <t xml:space="preserve"> Heung A Line Co.,Ltd. C/O Heung A LINE (THAILAND )CO.,LTD</t>
     </r>
   </si>
+  <si>
+    <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="2">
     <numFmt numFmtId="214" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="218" formatCode="[$-1010000]d/m/yyyy\ h:mm\ &quot;น.&quot;;@"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -294,15 +299,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="11"/>
@@ -340,6 +340,26 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF212121"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -354,20 +374,20 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +416,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -479,36 +504,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dotted">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -535,13 +538,35 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <right/>
+      <top style="dotted">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -560,25 +585,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -682,7 +704,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -703,94 +725,79 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -799,92 +806,77 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="214" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="214" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="13">
+  <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{AB109682-9817-40B2-83A1-11B2B700F361}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{42C7165A-2EF9-43D2-BDDD-39AB87C920CE}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{FAC7EF40-ADD4-44FD-8B28-35101187BFB1}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{D98A6BCC-C37F-4549-913A-AD80DB472E3E}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{7865FDCD-8191-4330-8A2B-5204AF6B59EC}"/>
-    <cellStyle name="Normal 2 2" xfId="7" xr:uid="{8A9F8AB1-71C8-43AC-AA28-797961015066}"/>
-    <cellStyle name="Normal 3" xfId="8" xr:uid="{58970540-505E-444B-955F-F4FF461F9797}"/>
-    <cellStyle name="Normal 4" xfId="9" xr:uid="{212CEF86-659F-4E0E-84A2-843BEB6D172D}"/>
-    <cellStyle name="จุลภาค 2" xfId="10" xr:uid="{5B9BCACA-57FC-4744-9634-6BA03194FA05}"/>
-    <cellStyle name="ปกติ 2" xfId="11" xr:uid="{FBA92230-82A7-41C1-AE97-326644BCB347}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="12" xr:uid="{BC3D26B1-E8A2-4BF5-97AE-B877125C7686}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{3B4484C8-AFEE-48B5-A4F6-1278E718C4BD}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{7C67419B-029E-4944-B034-F6BF09D9D0A0}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{DF980D57-6211-46C9-8326-B4FA356828A1}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{1CD9530B-0E4B-4262-92D0-12A32BC881A8}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{AD39F483-EDC7-4C6D-9226-A135D6B18B53}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{EB9B7624-010D-4E93-9F7B-6149C68E9CE0}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{D050879F-B631-40F8-B2E8-5CF4A1ECF33C}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{B219E8E2-CFC3-4FCA-96C5-BD1D4F898C81}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -902,7 +894,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>708660</xdr:colOff>
+      <xdr:colOff>701040</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
@@ -914,10 +906,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="549928" name="Rectangle 1">
+        <xdr:cNvPr id="447500" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186ED244-4BB4-99A1-BBAB-B0C6B3315959}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FFB4401-35A8-5383-6E20-598A2A201911}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -927,57 +919,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7048500" y="2202180"/>
-          <a:ext cx="1219200" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>297180</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="549929" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791B5E76-56EF-B118-7F14-37AE7830580D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3802380" y="2202180"/>
-          <a:ext cx="304800" cy="259080"/>
+          <a:off x="6499860" y="2202180"/>
+          <a:ext cx="762000" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1012,10 +955,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="549930" name="Rectangle 4">
+        <xdr:cNvPr id="447501" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EEEDEF-B0F8-7745-9B8A-7C8AD03B0771}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C73E196-C81F-73E9-DC4B-62DF1BE9DAA5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1049,22 +992,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>459061</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>303068</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="549931" name="Rectangle 4">
+        <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8DF977D-234D-FC77-E566-84C2AD518E6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E782299-893C-CB5E-DE6C-A373C2DC9D35}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1074,70 +1017,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="144780" y="2202180"/>
-          <a:ext cx="312420" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1359274</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>6387</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>302578</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>263957</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4459CB1B-2AE7-8F3B-CB71-DB705216909B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2019300" y="2133600"/>
-          <a:ext cx="350304" cy="264968"/>
+          <a:off x="152400" y="2190750"/>
+          <a:ext cx="352425" cy="257175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -1182,10 +1069,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="550960" name="Rectangle 1">
+        <xdr:cNvPr id="448536" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2734E3A-E438-D017-0334-2D18AF4488B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F357F9E-7FFE-0FBE-7202-BEB63B221A1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1219,7 +1106,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
@@ -1231,10 +1118,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="550961" name="Rectangle 2">
+        <xdr:cNvPr id="448537" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3E56AE8-F4ED-F7F8-F810-978560401FBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D13CA1-5A3E-9BDF-EBA4-CDABD9366D62}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1244,8 +1131,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3131820" y="2270760"/>
-          <a:ext cx="289560" cy="259080"/>
+          <a:off x="3124200" y="2270760"/>
+          <a:ext cx="297180" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1275,7 +1162,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
@@ -1287,10 +1174,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="550962" name="Rectangle 3">
+        <xdr:cNvPr id="448538" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{538537C7-25CC-0B49-5D54-36F942C0B40F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{414AC021-6FCD-29DB-DE13-226ADEC6EF9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1300,8 +1187,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="144780" y="2270760"/>
-          <a:ext cx="289560" cy="259080"/>
+          <a:off x="137160" y="2270760"/>
+          <a:ext cx="297180" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1336,10 +1223,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="550963" name="Rectangle 4">
+        <xdr:cNvPr id="448539" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBB08CDC-914F-6DE9-0824-9B4B64D7A17D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB0A9A73-0262-39AC-09A3-B57EB3F59C78}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1385,10 +1272,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="550964" name="Text Box 5">
+        <xdr:cNvPr id="448540" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA758CCB-FD85-5434-09F3-90170FE32AD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC79A505-A5B0-CC45-1579-7C5FCFBE0094}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1434,22 +1321,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>188595</xdr:colOff>
+      <xdr:colOff>196215</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>370027</xdr:colOff>
+      <xdr:colOff>371475</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>282687</xdr:rowOff>
+      <xdr:rowOff>276225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FE1C5CB-C4E8-9D27-013F-05BDDBB13E3F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48B76E1D-7CC8-DD29-B4D7-E2A2A98F4F6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1825,11 +1712,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663C9160-AC5A-471E-92FD-3642712AF67D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47046B40-072A-4430-9ACA-7F96625AE5BE}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="7.875" style="28" customWidth="1"/>
@@ -1838,33 +1725,35 @@
     <col min="4" max="4" width="8.375" style="28" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="28" customWidth="1"/>
     <col min="6" max="6" width="7.75" style="28" customWidth="1"/>
-    <col min="7" max="7" width="19.75" style="28" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="28" customWidth="1"/>
+    <col min="7" max="7" width="20.875" style="28" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="28" customWidth="1"/>
     <col min="9" max="9" width="6.25" style="28" customWidth="1"/>
-    <col min="10" max="10" width="31.625" style="28" customWidth="1"/>
-    <col min="11" max="11" width="6.375" style="28" customWidth="1"/>
-    <col min="12" max="12" width="66.625" style="28" customWidth="1"/>
-    <col min="13" max="13" width="21.625" style="28" customWidth="1"/>
-    <col min="14" max="16384" width="7.875" style="28"/>
+    <col min="10" max="10" width="24" style="28" customWidth="1"/>
+    <col min="11" max="11" width="8" style="28" customWidth="1"/>
+    <col min="12" max="12" width="7.875" style="28" customWidth="1"/>
+    <col min="13" max="13" width="36.375" style="28" customWidth="1"/>
+    <col min="14" max="14" width="21.625" style="28" customWidth="1"/>
+    <col min="15" max="16384" width="7.875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:13" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-    </row>
-    <row r="2" spans="1:15" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="59"/>
+    </row>
+    <row r="2" spans="1:13" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="21"/>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -1875,7 +1764,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:15" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
@@ -1888,7 +1777,7 @@
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="1:15" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:13" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
       <c r="A4" s="25" t="s">
         <v>24</v>
       </c>
@@ -1896,7 +1785,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:13" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
       <c r="A5" s="25" t="s">
         <v>24</v>
       </c>
@@ -1907,28 +1796,29 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:13" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
       <c r="A6" s="25"/>
     </row>
-    <row r="7" spans="1:15" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-    </row>
-    <row r="9" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="29" t="s">
         <v>3</v>
       </c>
@@ -1936,30 +1826,34 @@
       <c r="D9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="34" t="s">
         <v>5</v>
       </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
       <c r="K9" s="28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="49" t="s">
+    <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B10" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="34"/>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="50"/>
-      <c r="H10" s="28" t="s">
+      <c r="E10" s="34"/>
+      <c r="H10" s="34" t="s">
         <v>10</v>
       </c>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
       <c r="K10" s="28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
@@ -1968,58 +1862,60 @@
       <c r="E11" s="61"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-    </row>
-    <row r="12" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-    </row>
-    <row r="13" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C12" s="62"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+    </row>
+    <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-    </row>
-    <row r="14" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-    </row>
-    <row r="15" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+    </row>
+    <row r="15" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A16" s="43" t="s">
         <v>12</v>
       </c>
@@ -2053,407 +1949,1029 @@
       <c r="K16" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="51" t="s">
+      <c r="L16" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-    </row>
-    <row r="17" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="45"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="55"/>
+      <c r="M16" s="56"/>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="47"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="47"/>
       <c r="L17" s="53"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-    </row>
-    <row r="18" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="45"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="55"/>
+      <c r="M17" s="54"/>
+    </row>
+    <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="47"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="47"/>
       <c r="L18" s="53"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="47"/>
-      <c r="O18" s="47"/>
-    </row>
-    <row r="19" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="45"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="55"/>
+      <c r="M18" s="54"/>
+    </row>
+    <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="47"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="47"/>
       <c r="L19" s="53"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-    </row>
-    <row r="20" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="45"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="55"/>
+      <c r="M19" s="54"/>
+    </row>
+    <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="47"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="47"/>
       <c r="L20" s="53"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-    </row>
-    <row r="21" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="45"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="55"/>
+      <c r="M20" s="54"/>
+    </row>
+    <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="47"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="47"/>
       <c r="L21" s="53"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-    </row>
-    <row r="22" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="45"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="55"/>
+      <c r="M21" s="54"/>
+    </row>
+    <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="47"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="47"/>
       <c r="L22" s="53"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="47"/>
-    </row>
-    <row r="23" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="45"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="55"/>
+      <c r="M22" s="54"/>
+    </row>
+    <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="47"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="47"/>
       <c r="L23" s="53"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-    </row>
-    <row r="24" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="45"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="55"/>
+      <c r="M23" s="54"/>
+    </row>
+    <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="47"/>
       <c r="L24" s="53"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-    </row>
-    <row r="25" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="45"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="55"/>
+      <c r="M24" s="54"/>
+    </row>
+    <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="47"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="47"/>
       <c r="L25" s="53"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-    </row>
-    <row r="26" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="45"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="55"/>
+      <c r="M25" s="54"/>
+    </row>
+    <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="47"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="47"/>
       <c r="L26" s="53"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-    </row>
-    <row r="27" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="45"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-    </row>
-    <row r="28" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="45"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-    </row>
-    <row r="29" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="45"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-    </row>
-    <row r="30" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="45"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-    </row>
-    <row r="31" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="45"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="47"/>
-    </row>
-    <row r="32" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="45"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="47"/>
-      <c r="O32" s="47"/>
-    </row>
-    <row r="33" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="45"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-    </row>
-    <row r="34" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="69"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-    </row>
-    <row r="35" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="45"/>
-      <c r="B35" s="74"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-    </row>
-    <row r="37" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="73"/>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="73"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="72"/>
-    </row>
-    <row r="38" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="71" t="s">
+      <c r="M26" s="54"/>
+    </row>
+    <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="47"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="52"/>
+    </row>
+    <row r="28" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="47"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="52"/>
+    </row>
+    <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="66"/>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="47"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="70"/>
+    </row>
+    <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="68"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="67"/>
+    </row>
+    <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="H38" s="71" t="s">
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="H33" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="71"/>
-    </row>
-    <row r="39" spans="1:15" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="31" t="s">
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
+    </row>
+    <row r="34" spans="1:17" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B34" s="32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="31"/>
-      <c r="B40" s="32" t="s">
+    <row r="35" spans="1:17" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="31"/>
+      <c r="B35" s="32" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
+    </row>
+    <row r="49" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="44"/>
+    </row>
+    <row r="50" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+    </row>
+    <row r="51" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="45"/>
+      <c r="P51" s="45"/>
+      <c r="Q51" s="44"/>
+    </row>
+    <row r="52" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="44"/>
+    </row>
+    <row r="53" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="46"/>
+      <c r="M53" s="46"/>
+      <c r="N53" s="46"/>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="44"/>
+    </row>
+    <row r="54" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="46"/>
+      <c r="M54" s="46"/>
+      <c r="N54" s="46"/>
+      <c r="O54" s="46"/>
+      <c r="P54" s="46"/>
+      <c r="Q54" s="44"/>
+    </row>
+    <row r="55" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="46"/>
+      <c r="O55" s="46"/>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="44"/>
+    </row>
+    <row r="56" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="46"/>
+      <c r="M56" s="46"/>
+      <c r="N56" s="46"/>
+      <c r="O56" s="46"/>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="44"/>
+    </row>
+    <row r="57" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="46"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="46"/>
+      <c r="K57" s="46"/>
+      <c r="L57" s="46"/>
+      <c r="M57" s="46"/>
+      <c r="N57" s="46"/>
+      <c r="O57" s="46"/>
+      <c r="P57" s="46"/>
+      <c r="Q57" s="44"/>
+    </row>
+    <row r="58" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="46"/>
+      <c r="M58" s="46"/>
+      <c r="N58" s="46"/>
+      <c r="O58" s="46"/>
+      <c r="P58" s="46"/>
+      <c r="Q58" s="44"/>
+    </row>
+    <row r="59" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="46"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
+      <c r="L59" s="46"/>
+      <c r="M59" s="46"/>
+      <c r="N59" s="46"/>
+      <c r="O59" s="46"/>
+      <c r="P59" s="46"/>
+      <c r="Q59" s="44"/>
+    </row>
+    <row r="60" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
+      <c r="M60" s="46"/>
+      <c r="N60" s="46"/>
+      <c r="O60" s="46"/>
+      <c r="P60" s="46"/>
+      <c r="Q60" s="44"/>
+    </row>
+    <row r="61" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46"/>
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
+      <c r="M61" s="46"/>
+      <c r="N61" s="46"/>
+      <c r="O61" s="46"/>
+      <c r="P61" s="46"/>
+      <c r="Q61" s="44"/>
+    </row>
+    <row r="62" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
+      <c r="K62" s="46"/>
+      <c r="L62" s="46"/>
+      <c r="M62" s="46"/>
+      <c r="N62" s="46"/>
+      <c r="O62" s="46"/>
+      <c r="P62" s="46"/>
+      <c r="Q62" s="44"/>
+    </row>
+    <row r="63" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="46"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="46"/>
+      <c r="L63" s="46"/>
+      <c r="M63" s="46"/>
+      <c r="N63" s="46"/>
+      <c r="O63" s="46"/>
+      <c r="P63" s="46"/>
+      <c r="Q63" s="44"/>
+    </row>
+    <row r="64" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="46"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="46"/>
+      <c r="O64" s="46"/>
+      <c r="P64" s="46"/>
+      <c r="Q64" s="44"/>
+    </row>
+    <row r="65" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="46"/>
+      <c r="I65" s="46"/>
+      <c r="J65" s="46"/>
+      <c r="K65" s="46"/>
+      <c r="L65" s="46"/>
+      <c r="M65" s="46"/>
+      <c r="N65" s="46"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="46"/>
+      <c r="Q65" s="44"/>
+    </row>
+    <row r="66" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="46"/>
+      <c r="K66" s="46"/>
+      <c r="L66" s="46"/>
+      <c r="M66" s="46"/>
+      <c r="N66" s="46"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="46"/>
+      <c r="Q66" s="44"/>
+    </row>
+    <row r="67" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="46"/>
+      <c r="N67" s="46"/>
+      <c r="O67" s="46"/>
+      <c r="P67" s="46"/>
+      <c r="Q67" s="44"/>
+    </row>
+    <row r="68" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
+      <c r="L68" s="46"/>
+      <c r="M68" s="46"/>
+      <c r="N68" s="46"/>
+      <c r="O68" s="46"/>
+      <c r="P68" s="46"/>
+      <c r="Q68" s="44"/>
+    </row>
+    <row r="69" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="46"/>
+      <c r="I69" s="46"/>
+      <c r="J69" s="46"/>
+      <c r="K69" s="46"/>
+      <c r="L69" s="46"/>
+      <c r="M69" s="46"/>
+      <c r="N69" s="46"/>
+      <c r="O69" s="46"/>
+      <c r="P69" s="46"/>
+      <c r="Q69" s="44"/>
+    </row>
+    <row r="70" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="46"/>
+      <c r="M70" s="46"/>
+      <c r="N70" s="46"/>
+      <c r="O70" s="46"/>
+      <c r="P70" s="46"/>
+      <c r="Q70" s="44"/>
+    </row>
+    <row r="71" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="46"/>
+      <c r="N71" s="46"/>
+      <c r="O71" s="46"/>
+      <c r="P71" s="46"/>
+      <c r="Q71" s="44"/>
+    </row>
+    <row r="72" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="46"/>
+      <c r="M72" s="46"/>
+      <c r="N72" s="46"/>
+      <c r="O72" s="46"/>
+      <c r="P72" s="46"/>
+      <c r="Q72" s="44"/>
+    </row>
+    <row r="73" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="46"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="46"/>
+      <c r="M73" s="46"/>
+      <c r="N73" s="46"/>
+      <c r="O73" s="46"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="44"/>
+    </row>
+    <row r="74" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="46"/>
+      <c r="J74" s="46"/>
+      <c r="K74" s="46"/>
+      <c r="L74" s="46"/>
+      <c r="M74" s="46"/>
+      <c r="N74" s="46"/>
+      <c r="O74" s="46"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="44"/>
+    </row>
+    <row r="75" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D75" s="44"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="46"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="46"/>
+      <c r="M75" s="46"/>
+      <c r="N75" s="46"/>
+      <c r="O75" s="46"/>
+      <c r="P75" s="46"/>
+      <c r="Q75" s="44"/>
+    </row>
+    <row r="76" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="46"/>
+      <c r="M76" s="46"/>
+      <c r="N76" s="46"/>
+      <c r="O76" s="46"/>
+      <c r="P76" s="46"/>
+      <c r="Q76" s="44"/>
+    </row>
+    <row r="77" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="46"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="46"/>
+      <c r="I77" s="46"/>
+      <c r="J77" s="46"/>
+      <c r="K77" s="46"/>
+      <c r="L77" s="46"/>
+      <c r="M77" s="46"/>
+      <c r="N77" s="46"/>
+      <c r="O77" s="46"/>
+      <c r="P77" s="46"/>
+      <c r="Q77" s="44"/>
+    </row>
+    <row r="78" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46"/>
+      <c r="M78" s="46"/>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="44"/>
+    </row>
+    <row r="79" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
+      <c r="M79" s="46"/>
+      <c r="N79" s="46"/>
+      <c r="O79" s="46"/>
+      <c r="P79" s="46"/>
+      <c r="Q79" s="44"/>
+    </row>
+    <row r="80" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="46"/>
+      <c r="M80" s="46"/>
+      <c r="N80" s="46"/>
+      <c r="O80" s="46"/>
+      <c r="P80" s="46"/>
+      <c r="Q80" s="44"/>
+    </row>
+    <row r="81" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="46"/>
+      <c r="G81" s="46"/>
+      <c r="H81" s="46"/>
+      <c r="I81" s="46"/>
+      <c r="J81" s="46"/>
+      <c r="K81" s="46"/>
+      <c r="L81" s="46"/>
+      <c r="M81" s="46"/>
+      <c r="N81" s="46"/>
+      <c r="O81" s="46"/>
+      <c r="P81" s="46"/>
+      <c r="Q81" s="44"/>
+    </row>
+    <row r="82" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="46"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="46"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="46"/>
+      <c r="M82" s="46"/>
+      <c r="N82" s="46"/>
+      <c r="O82" s="46"/>
+      <c r="P82" s="46"/>
+      <c r="Q82" s="44"/>
+    </row>
+    <row r="83" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="46"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="46"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
+      <c r="N83" s="46"/>
+      <c r="O83" s="46"/>
+      <c r="P83" s="46"/>
+      <c r="Q83" s="44"/>
+    </row>
+    <row r="84" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="46"/>
+      <c r="H84" s="46"/>
+      <c r="I84" s="46"/>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
+      <c r="L84" s="46"/>
+      <c r="M84" s="46"/>
+      <c r="N84" s="46"/>
+      <c r="O84" s="46"/>
+      <c r="P84" s="46"/>
+      <c r="Q84" s="44"/>
+    </row>
+    <row r="85" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="46"/>
+      <c r="G85" s="46"/>
+      <c r="H85" s="46"/>
+      <c r="I85" s="46"/>
+      <c r="J85" s="46"/>
+      <c r="K85" s="46"/>
+      <c r="L85" s="46"/>
+      <c r="M85" s="46"/>
+      <c r="N85" s="46"/>
+      <c r="O85" s="46"/>
+      <c r="P85" s="46"/>
+      <c r="Q85" s="44"/>
+    </row>
+    <row r="86" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="46"/>
+      <c r="H86" s="46"/>
+      <c r="I86" s="46"/>
+      <c r="J86" s="46"/>
+      <c r="K86" s="46"/>
+      <c r="L86" s="46"/>
+      <c r="M86" s="46"/>
+      <c r="N86" s="46"/>
+      <c r="O86" s="46"/>
+      <c r="P86" s="46"/>
+      <c r="Q86" s="44"/>
+    </row>
+    <row r="87" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D87" s="44"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="46"/>
+      <c r="G87" s="46"/>
+      <c r="H87" s="46"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="46"/>
+      <c r="K87" s="46"/>
+      <c r="L87" s="46"/>
+      <c r="M87" s="46"/>
+      <c r="N87" s="46"/>
+      <c r="O87" s="46"/>
+      <c r="P87" s="46"/>
+      <c r="Q87" s="44"/>
+    </row>
+    <row r="88" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D88" s="44"/>
+      <c r="E88" s="44"/>
+      <c r="F88" s="46"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="46"/>
+      <c r="I88" s="46"/>
+      <c r="J88" s="46"/>
+      <c r="K88" s="46"/>
+      <c r="L88" s="46"/>
+      <c r="M88" s="46"/>
+      <c r="N88" s="46"/>
+      <c r="O88" s="46"/>
+      <c r="P88" s="46"/>
+      <c r="Q88" s="44"/>
+    </row>
+    <row r="89" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D89" s="44"/>
+      <c r="E89" s="44"/>
+      <c r="F89" s="46"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="46"/>
+      <c r="I89" s="46"/>
+      <c r="J89" s="46"/>
+      <c r="K89" s="46"/>
+      <c r="L89" s="46"/>
+      <c r="M89" s="46"/>
+      <c r="N89" s="46"/>
+      <c r="O89" s="46"/>
+      <c r="P89" s="46"/>
+      <c r="Q89" s="44"/>
+    </row>
+    <row r="90" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="46"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="46"/>
+      <c r="M90" s="46"/>
+      <c r="N90" s="46"/>
+      <c r="O90" s="46"/>
+      <c r="P90" s="46"/>
+      <c r="Q90" s="44"/>
+    </row>
+    <row r="91" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="46"/>
+      <c r="K91" s="46"/>
+      <c r="L91" s="46"/>
+      <c r="M91" s="46"/>
+      <c r="N91" s="46"/>
+      <c r="O91" s="46"/>
+      <c r="P91" s="46"/>
+      <c r="Q91" s="44"/>
+    </row>
+    <row r="92" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="46"/>
+      <c r="G92" s="46"/>
+      <c r="H92" s="46"/>
+      <c r="I92" s="46"/>
+      <c r="J92" s="46"/>
+      <c r="K92" s="46"/>
+      <c r="L92" s="46"/>
+      <c r="M92" s="46"/>
+      <c r="N92" s="46"/>
+      <c r="O92" s="46"/>
+      <c r="P92" s="46"/>
+      <c r="Q92" s="44"/>
+    </row>
+    <row r="93" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="44"/>
+      <c r="J93" s="44"/>
+      <c r="K93" s="44"/>
+      <c r="L93" s="44"/>
+      <c r="M93" s="44"/>
+      <c r="N93" s="44"/>
+      <c r="O93" s="44"/>
+      <c r="P93" s="44"/>
+      <c r="Q93" s="44"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="H38:L38"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="H37:L37"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B7:L7"/>
-    <mergeCell ref="C12:L12"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="A34:L34"/>
+  <mergeCells count="14">
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="C11:M11"/>
+    <mergeCell ref="C12:M12"/>
+    <mergeCell ref="C13:M13"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B17:B33">
-    <cfRule type="duplicateValues" dxfId="1" priority="22" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="56" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5302FEC-CB8C-47FE-9F79-E90F41349A7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89761AB7-0275-404C-99CD-7FDFC4234391}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -2471,21 +2989,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="84"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="81"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4"/>
@@ -2500,10 +3018,10 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="86"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="8" t="s">
         <v>25</v>
       </c>
@@ -2514,19 +3032,19 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="89"/>
+      <c r="B4" s="76"/>
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="89"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
@@ -2539,23 +3057,23 @@
       <c r="B6" s="11"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87" t="s">
+      <c r="B7" s="82"/>
+      <c r="C7" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="87"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="6" t="s">
@@ -2590,31 +3108,31 @@
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2" t="s">
@@ -2626,11 +3144,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="81">
+      <c r="H13" s="87">
         <v>38155</v>
       </c>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
@@ -2642,11 +3160,11 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="81">
+      <c r="H14" s="87">
         <v>38155</v>
       </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
@@ -2656,10 +3174,10 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="78"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
@@ -2684,17 +3202,17 @@
       <c r="K16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="79" t="s">
+      <c r="L16" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="80"/>
+      <c r="M16" s="86"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -2703,16 +3221,16 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <f t="shared" ref="A18:A31" si="0">A17+1</f>
         <v>2</v>
       </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -2721,16 +3239,16 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -2739,16 +3257,16 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="75"/>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -2757,16 +3275,16 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -2775,16 +3293,16 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="75"/>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -2793,16 +3311,16 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -2811,16 +3329,16 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -2829,16 +3347,16 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -2847,16 +3365,16 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -2865,16 +3383,16 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -2883,16 +3401,16 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2901,16 +3419,16 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -2919,16 +3437,16 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="78"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="75"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B30" s="78"/>
-      <c r="C30" s="78"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -2937,16 +3455,16 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="78"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="75"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B31" s="78"/>
-      <c r="C31" s="78"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -2955,36 +3473,36 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="85"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="78"/>
+      <c r="L33" s="78"/>
+      <c r="M33" s="78"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="88" t="s">
+      <c r="A34" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="I34" s="88" t="s">
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="I34" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="15" t="s">
@@ -3008,6 +3526,42 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="L20:M20"/>
@@ -3018,42 +3572,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{764ECBDF-7D7D-4A43-A1A8-7B48F658F6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AEF0E40-493C-4FD0-8069-C971012C3B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{48D7D643-5868-48BC-BF38-53AD3B19D4F6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39DCA305-E5F9-4921-B79C-F0C01E5EE668}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
@@ -867,14 +867,14 @@
   <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{3B4484C8-AFEE-48B5-A4F6-1278E718C4BD}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{7C67419B-029E-4944-B034-F6BF09D9D0A0}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{DF980D57-6211-46C9-8326-B4FA356828A1}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{1CD9530B-0E4B-4262-92D0-12A32BC881A8}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{AD39F483-EDC7-4C6D-9226-A135D6B18B53}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{EB9B7624-010D-4E93-9F7B-6149C68E9CE0}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{D050879F-B631-40F8-B2E8-5CF4A1ECF33C}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{B219E8E2-CFC3-4FCA-96C5-BD1D4F898C81}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{D558A7B0-F383-4A45-9874-0D172B72E595}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{354A18FA-40BC-49FB-B0A1-CCC10D2B4994}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{CC859A9B-7177-43C3-B993-30394A1662F1}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{9CFA8072-F5CB-4AFA-871D-49B4BD6F6504}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EDF9C388-140A-459A-A97F-EBE496FD5A67}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{A43328B8-9C84-461F-8DF9-A40D188E6C3F}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{143F1699-2C59-4F0D-87D9-81EC0882B095}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{D79B28C4-1BE4-4508-B385-766C7C1F4D8E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -894,22 +894,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701040</xdr:colOff>
+      <xdr:colOff>563880</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>297180</xdr:rowOff>
+      <xdr:rowOff>236220</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="447500" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FFB4401-35A8-5383-6E20-598A2A201911}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFA8FB5-74F6-65D4-2B31-99CA8F949C9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -919,8 +919,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6499860" y="2202180"/>
-          <a:ext cx="762000" cy="259080"/>
+          <a:off x="6362700" y="2194560"/>
+          <a:ext cx="899160" cy="205740"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -943,22 +943,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:colOff>1097280</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>289560</xdr:rowOff>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>243840</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>236220</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="447501" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C73E196-C81F-73E9-DC4B-62DF1BE9DAA5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6FEA759-A6F5-C917-B63A-D37EBCFF4A97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -968,8 +968,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1851660" y="2148840"/>
-          <a:ext cx="320040" cy="251460"/>
+          <a:off x="1577340" y="2087880"/>
+          <a:ext cx="533400" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -992,22 +992,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>102870</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>459061</xdr:colOff>
+      <xdr:colOff>366541</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>303068</xdr:rowOff>
+      <xdr:rowOff>250025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E782299-893C-CB5E-DE6C-A373C2DC9D35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A876B48F-5752-0A3F-473B-BF28EADBE22D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1057,22 +1057,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>243840</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
+      <xdr:colOff>472440</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="448536" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F357F9E-7FFE-0FBE-7202-BEB63B221A1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77B31A87-B9D9-EF4A-E5BB-83DA524AC4EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1082,8 +1082,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4953000" y="2278380"/>
-          <a:ext cx="289560" cy="259080"/>
+          <a:off x="4892040" y="2255520"/>
+          <a:ext cx="228600" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1106,22 +1106,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>106680</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
+      <xdr:colOff>342900</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="448537" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D13CA1-5A3E-9BDF-EBA4-CDABD9366D62}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB82C07-E13B-EB49-3B36-ABD6BF030DA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1131,8 +1131,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3124200" y="2270760"/>
-          <a:ext cx="297180" cy="259080"/>
+          <a:off x="3093720" y="2247900"/>
+          <a:ext cx="236220" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1162,22 +1162,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>106680</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
+      <xdr:colOff>342900</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="448538" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{414AC021-6FCD-29DB-DE13-226ADEC6EF9C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80765AA0-2AE2-60A6-8527-A71A5FDC6727}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1187,8 +1187,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="137160" y="2270760"/>
-          <a:ext cx="297180" cy="259080"/>
+          <a:off x="106680" y="2247900"/>
+          <a:ext cx="236220" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1211,22 +1211,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
+      <xdr:colOff>426720</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>830580</xdr:colOff>
+      <xdr:colOff>662940</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="448539" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB0A9A73-0262-39AC-09A3-B57EB3F59C78}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1665BDA9-4435-647D-4E5B-CB937025B82E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1236,8 +1236,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1493520" y="2278380"/>
-          <a:ext cx="297180" cy="259080"/>
+          <a:off x="1386840" y="2255520"/>
+          <a:ext cx="236220" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1260,22 +1260,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>335280</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="448540" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC79A505-A5B0-CC45-1579-7C5FCFBE0094}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8620EB36-62BA-FBF9-B71B-9D69FC7623E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1285,8 +1285,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2926080" y="3688080"/>
-          <a:ext cx="99060" cy="335280"/>
+          <a:off x="2842260" y="3688080"/>
+          <a:ext cx="175260" cy="327660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1321,22 +1321,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>196215</xdr:colOff>
+      <xdr:colOff>160020</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
+      <xdr:colOff>294198</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>276225</xdr:rowOff>
+      <xdr:rowOff>218291</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48B76E1D-7CC8-DD29-B4D7-E2A2A98F4F6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0061BB9C-0003-2E3C-3577-76E1D6BF5FBF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1712,7 +1712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47046B40-072A-4430-9ACA-7F96625AE5BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B75919-EDA3-4DAA-B796-5A8DA487422E}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2971,7 +2971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89761AB7-0275-404C-99CD-7FDFC4234391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF068020-1530-4955-8954-861401A72499}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AEF0E40-493C-4FD0-8069-C971012C3B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8C9970-A7E7-4BA3-8D6A-3560CBFE493B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39DCA305-E5F9-4921-B79C-F0C01E5EE668}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{070B9A69-FE81-4CAB-9F6F-23BE266B21E0}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
@@ -368,6 +368,13 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
@@ -376,13 +383,6 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
@@ -491,52 +491,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="dotted">
@@ -584,6 +538,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -600,7 +600,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -752,31 +752,58 @@
     <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -785,64 +812,37 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="214" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,30 +851,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="214" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{D558A7B0-F383-4A45-9874-0D172B72E595}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{354A18FA-40BC-49FB-B0A1-CCC10D2B4994}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{CC859A9B-7177-43C3-B993-30394A1662F1}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{9CFA8072-F5CB-4AFA-871D-49B4BD6F6504}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EDF9C388-140A-459A-A97F-EBE496FD5A67}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{A43328B8-9C84-461F-8DF9-A40D188E6C3F}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{143F1699-2C59-4F0D-87D9-81EC0882B095}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{D79B28C4-1BE4-4508-B385-766C7C1F4D8E}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{7B754249-F3FA-4DBC-9291-1568C7D22C47}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{BB1C9D58-9BD0-4785-922B-4A0E8F5F2584}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{B434D44F-CB06-48B7-92CF-225E1C57FD41}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{75528142-734B-4C9B-921D-C0AE90A802A7}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{1E88A86F-3D73-4861-B1A5-DE609B9A96F6}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{D2A936DB-DAFB-45CC-8F0C-3A7373417C95}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{B5133AB6-4CD5-4117-9532-F6D0943E411B}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{CB80B04C-37B1-4866-9727-C8FA8C7CF07F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -906,10 +900,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447500" name="Rectangle 1">
+        <xdr:cNvPr id="447503" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFA8FB5-74F6-65D4-2B31-99CA8F949C9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8691C3E-E0CF-C85C-21ED-C03BC665A566}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -955,10 +949,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447501" name="Rectangle 4">
+        <xdr:cNvPr id="447504" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6FEA759-A6F5-C917-B63A-D37EBCFF4A97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0EBA9F-003B-EF63-F034-40574BB48A7F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1007,7 +1001,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A876B48F-5752-0A3F-473B-BF28EADBE22D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBFCCC9A-4DE8-F184-B977-A48BC6DF1E65}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1069,10 +1063,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448536" name="Rectangle 1">
+        <xdr:cNvPr id="448542" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77B31A87-B9D9-EF4A-E5BB-83DA524AC4EB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64D112AC-D363-D263-4C1E-F8126D90C9C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1118,10 +1112,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448537" name="Rectangle 2">
+        <xdr:cNvPr id="448543" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB82C07-E13B-EB49-3B36-ABD6BF030DA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFD289E6-A149-AC6D-7BD5-C7251AF36D08}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1174,10 +1168,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448538" name="Rectangle 3">
+        <xdr:cNvPr id="448544" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80765AA0-2AE2-60A6-8527-A71A5FDC6727}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F038283C-707E-A5AA-795B-E426E7711E22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1223,10 +1217,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448539" name="Rectangle 4">
+        <xdr:cNvPr id="448545" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1665BDA9-4435-647D-4E5B-CB937025B82E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A4EB52A-6A79-0F4A-31C4-252643C315A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1272,10 +1266,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448540" name="Text Box 5">
+        <xdr:cNvPr id="448546" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8620EB36-62BA-FBF9-B71B-9D69FC7623E3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A65D8CF6-79B3-12D8-E6A7-9021D4EBC3FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1336,7 +1330,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0061BB9C-0003-2E3C-3577-76E1D6BF5FBF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D2D6B6-79DD-ECD0-B2FE-8EB41808D0DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1712,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B75919-EDA3-4DAA-B796-5A8DA487422E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9105319-F78C-4894-8391-534D98AED004}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1737,21 +1731,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="21"/>
@@ -1803,20 +1797,20 @@
       <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="29" t="s">
@@ -1857,62 +1851,62 @@
       <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
     </row>
     <row r="15" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.6">
@@ -1949,10 +1943,10 @@
       <c r="K16" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="56" t="s">
+      <c r="L16" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="56"/>
+      <c r="M16" s="65"/>
     </row>
     <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="47"/>
@@ -1966,8 +1960,8 @@
       <c r="I17" s="37"/>
       <c r="J17" s="48"/>
       <c r="K17" s="47"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="54"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="52"/>
     </row>
     <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="47"/>
@@ -1981,8 +1975,8 @@
       <c r="I18" s="37"/>
       <c r="J18" s="48"/>
       <c r="K18" s="47"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="54"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="52"/>
     </row>
     <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="47"/>
@@ -1996,8 +1990,8 @@
       <c r="I19" s="37"/>
       <c r="J19" s="48"/>
       <c r="K19" s="47"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="54"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="52"/>
     </row>
     <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="47"/>
@@ -2011,8 +2005,8 @@
       <c r="I20" s="37"/>
       <c r="J20" s="48"/>
       <c r="K20" s="47"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="54"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="52"/>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="47"/>
@@ -2026,8 +2020,8 @@
       <c r="I21" s="37"/>
       <c r="J21" s="48"/>
       <c r="K21" s="47"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="52"/>
     </row>
     <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="47"/>
@@ -2041,8 +2035,8 @@
       <c r="I22" s="37"/>
       <c r="J22" s="48"/>
       <c r="K22" s="47"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="54"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="52"/>
     </row>
     <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="47"/>
@@ -2056,8 +2050,8 @@
       <c r="I23" s="37"/>
       <c r="J23" s="48"/>
       <c r="K23" s="47"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="54"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="52"/>
     </row>
     <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="47"/>
@@ -2071,8 +2065,8 @@
       <c r="I24" s="37"/>
       <c r="J24" s="48"/>
       <c r="K24" s="47"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="52"/>
     </row>
     <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="47"/>
@@ -2086,8 +2080,8 @@
       <c r="I25" s="37"/>
       <c r="J25" s="48"/>
       <c r="K25" s="47"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="52"/>
     </row>
     <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="47"/>
@@ -2101,8 +2095,8 @@
       <c r="I26" s="37"/>
       <c r="J26" s="48"/>
       <c r="K26" s="47"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="54"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="52"/>
     </row>
     <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="47"/>
@@ -2135,64 +2129,64 @@
       <c r="M28" s="52"/>
     </row>
     <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="66"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="55"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="47"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="70"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="59"/>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="68"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67"/>
-      <c r="L32" s="67"/>
-      <c r="M32" s="67"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="74" t="s">
+      <c r="A33" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="H33" s="74" t="s">
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="H33" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
     </row>
     <row r="34" spans="1:17" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A34" s="31" t="s">
@@ -2945,7 +2939,14 @@
       <c r="Q93" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="26">
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="C11:M11"/>
+    <mergeCell ref="C12:M12"/>
+    <mergeCell ref="C13:M13"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="H32:M32"/>
     <mergeCell ref="A32:D32"/>
@@ -2953,13 +2954,18 @@
     <mergeCell ref="B30:K30"/>
     <mergeCell ref="H33:M33"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="C11:M11"/>
-    <mergeCell ref="C12:M12"/>
-    <mergeCell ref="C13:M13"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2971,7 +2977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF068020-1530-4955-8954-861401A72499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24B6ED9-B307-40A4-BD45-17118A9695FD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -2989,21 +2995,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="80"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4"/>
@@ -3032,19 +3038,19 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="76"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="76"/>
+      <c r="B5" s="85"/>
       <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
@@ -3108,31 +3114,31 @@
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2" t="s">
@@ -3144,11 +3150,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="87">
+      <c r="H13" s="77">
         <v>38155</v>
       </c>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
@@ -3160,11 +3166,11 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="87">
+      <c r="H14" s="77">
         <v>38155</v>
       </c>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
@@ -3174,10 +3180,10 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="75"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
@@ -3202,17 +3208,17 @@
       <c r="K16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="85" t="s">
+      <c r="L16" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="86"/>
+      <c r="M16" s="76"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -3221,16 +3227,16 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="75"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="74"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <f t="shared" ref="A18:A31" si="0">A17+1</f>
         <v>2</v>
       </c>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -3239,16 +3245,16 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="75"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="74"/>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B19" s="75"/>
-      <c r="C19" s="75"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -3257,16 +3263,16 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="75"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="74"/>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="75"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -3275,16 +3281,16 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -3293,16 +3299,16 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B22" s="75"/>
-      <c r="C22" s="75"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -3311,16 +3317,16 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -3329,16 +3335,16 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="75"/>
-      <c r="M23" s="75"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="74"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -3347,16 +3353,16 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -3365,16 +3371,16 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B26" s="75"/>
-      <c r="C26" s="75"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -3383,16 +3389,16 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B27" s="75"/>
-      <c r="C27" s="75"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -3401,16 +3407,16 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B28" s="75"/>
-      <c r="C28" s="75"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -3419,16 +3425,16 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="75"/>
-      <c r="M28" s="75"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -3437,16 +3443,16 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="75"/>
-      <c r="M29" s="75"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B30" s="75"/>
-      <c r="C30" s="75"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -3455,16 +3461,16 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="75"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B31" s="75"/>
-      <c r="C31" s="75"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -3473,36 +3479,36 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="78"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
-      <c r="M33" s="78"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="77" t="s">
+      <c r="A34" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="I34" s="77" t="s">
+      <c r="B34" s="84"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="I34" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
-      <c r="L34" s="77"/>
-      <c r="M34" s="77"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="84"/>
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="15" t="s">
@@ -3526,22 +3532,26 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A3:B3"/>
@@ -3552,26 +3562,22 @@
     <mergeCell ref="L24:M24"/>
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L21:M21"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8C9970-A7E7-4BA3-8D6A-3560CBFE493B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B08C3E6A-E517-477D-9C76-7C13C4501F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{070B9A69-FE81-4CAB-9F6F-23BE266B21E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BD95AD2-BDB8-44AE-8EA5-1440BB532832}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
@@ -861,14 +861,14 @@
   <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{7B754249-F3FA-4DBC-9291-1568C7D22C47}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{BB1C9D58-9BD0-4785-922B-4A0E8F5F2584}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{B434D44F-CB06-48B7-92CF-225E1C57FD41}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{75528142-734B-4C9B-921D-C0AE90A802A7}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{1E88A86F-3D73-4861-B1A5-DE609B9A96F6}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{D2A936DB-DAFB-45CC-8F0C-3A7373417C95}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{B5133AB6-4CD5-4117-9532-F6D0943E411B}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{CB80B04C-37B1-4866-9727-C8FA8C7CF07F}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{28EA4CF7-F074-4AB9-B5CF-7CB12E24A428}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{8B50A289-7BD1-4FBA-9E4E-D209F06FFD0A}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{4C853392-F2AA-48C0-8ADD-4C9B9AFEF7AD}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{92E212BD-D87A-4421-ACD2-A2E9511F98A3}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{12953AB6-E883-4C03-83B6-DCA8DDD7437F}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{2B6807E4-9FA9-41E7-9858-899206CF2931}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{AB3387F2-ABF1-468B-9076-44F855C5F6D8}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{C895C98E-2ED6-45A1-BE55-E28EAA7C2FEE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -903,7 +903,7 @@
         <xdr:cNvPr id="447503" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8691C3E-E0CF-C85C-21ED-C03BC665A566}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5D5E187-985E-9E3D-D7F2-8625A38976AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -952,7 +952,7 @@
         <xdr:cNvPr id="447504" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0EBA9F-003B-EF63-F034-40574BB48A7F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7480CD90-EBB3-5104-48FE-0D114F70206D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1001,7 +1001,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBFCCC9A-4DE8-F184-B977-A48BC6DF1E65}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9E76039-53AF-1B4B-75C7-D64F3E338EBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1066,7 +1066,7 @@
         <xdr:cNvPr id="448542" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64D112AC-D363-D263-4C1E-F8126D90C9C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89793061-C950-02BC-1819-F6BAAD9D67D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1115,7 +1115,7 @@
         <xdr:cNvPr id="448543" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFD289E6-A149-AC6D-7BD5-C7251AF36D08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E5C317B-67AC-E37E-EBBE-C8C6C58C1A2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1171,7 +1171,7 @@
         <xdr:cNvPr id="448544" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F038283C-707E-A5AA-795B-E426E7711E22}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB10FD1-BDFB-73DD-D3AD-3F43273C20D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1220,7 +1220,7 @@
         <xdr:cNvPr id="448545" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A4EB52A-6A79-0F4A-31C4-252643C315A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9B4619D-4E7C-8901-3551-8339150D3030}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="448546" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A65D8CF6-79B3-12D8-E6A7-9021D4EBC3FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B5E4C2C-E159-CA56-AF89-CEF9FBF3277D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1330,7 +1330,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D2D6B6-79DD-ECD0-B2FE-8EB41808D0DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9188E755-44AF-0AD3-83DC-D34BF40CC5EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9105319-F78C-4894-8391-534D98AED004}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790DBD09-F7D2-4B97-9332-740FFB20C498}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2977,7 +2977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24B6ED9-B307-40A4-BD45-17118A9695FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7485F-3311-405B-9ABA-E42213A80AA0}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B08C3E6A-E517-477D-9C76-7C13C4501F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DC0858E-89F8-4C05-ADAC-17B0E5149A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BD95AD2-BDB8-44AE-8EA5-1440BB532832}"/>
+    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{E9A8F0B2-F75E-4977-8CF6-0720706289C5}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
     <sheet name="CHORE CFS" sheetId="7" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CHORE CY'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CHORE CY'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>GATE IN / GATE OUT REQUEST</t>
   </si>
@@ -176,6 +176,15 @@
   <si>
     <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
   </si>
+  <si>
+    <t>E-MAIL</t>
+  </si>
+  <si>
+    <t>CONTACT / TEL NO.</t>
+  </si>
+  <si>
+    <t>CASH</t>
+  </si>
 </sst>
 </file>
 
@@ -185,7 +194,7 @@
     <numFmt numFmtId="214" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="218" formatCode="[$-1010000]d/m/yyyy\ h:mm\ &quot;น.&quot;;@"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -305,6 +314,12 @@
       <charset val="222"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -368,13 +383,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
@@ -383,6 +391,13 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
@@ -491,6 +506,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="dotted">
@@ -538,69 +599,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -704,7 +719,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -725,7 +740,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -734,76 +749,43 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="24" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -812,63 +794,105 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="214" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="214" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{28EA4CF7-F074-4AB9-B5CF-7CB12E24A428}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{8B50A289-7BD1-4FBA-9E4E-D209F06FFD0A}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{4C853392-F2AA-48C0-8ADD-4C9B9AFEF7AD}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{92E212BD-D87A-4421-ACD2-A2E9511F98A3}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{12953AB6-E883-4C03-83B6-DCA8DDD7437F}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{2B6807E4-9FA9-41E7-9858-899206CF2931}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{AB3387F2-ABF1-468B-9076-44F855C5F6D8}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{C895C98E-2ED6-45A1-BE55-E28EAA7C2FEE}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{717C8F23-486C-44C6-A90B-F8202DE11CF0}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{772D924A-BE3D-4807-A50A-F007D2BDA99B}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{F6F63994-74B6-43FB-8EFC-A8CB30903437}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{4A691EEE-C59C-45E9-B150-7163AA3658AF}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EB26CB89-3DBA-4939-87EC-B0F31E568BB6}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{28CBBCC1-F50D-4E20-948E-9ACCD4A6903B}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{A629EC5D-059A-4169-A445-ABEEB3C77DA7}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{04C086D6-7A37-4E43-A2ED-B89690D7DC37}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -900,10 +924,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447503" name="Rectangle 1">
+        <xdr:cNvPr id="447506" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5D5E187-985E-9E3D-D7F2-8625A38976AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{643A353F-BB83-BB5F-D019-B194ED2A58D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -949,10 +973,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447504" name="Rectangle 4">
+        <xdr:cNvPr id="447507" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7480CD90-EBB3-5104-48FE-0D114F70206D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F67CD93-072F-D187-477B-F5A5759E7DC1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1001,7 +1025,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9E76039-53AF-1B4B-75C7-D64F3E338EBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F8A684B-37F2-7019-D4EC-38375DF32198}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1063,10 +1087,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448542" name="Rectangle 1">
+        <xdr:cNvPr id="448548" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89793061-C950-02BC-1819-F6BAAD9D67D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E8EDB46-27EF-9728-EFDF-156E315928DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1112,10 +1136,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448543" name="Rectangle 2">
+        <xdr:cNvPr id="448549" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E5C317B-67AC-E37E-EBBE-C8C6C58C1A2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0FB2B7-A5AF-EE88-CB6F-459251682708}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1168,10 +1192,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448544" name="Rectangle 3">
+        <xdr:cNvPr id="448550" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB10FD1-BDFB-73DD-D3AD-3F43273C20D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C690E942-0919-F250-DFF3-94C12BD57CC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1217,10 +1241,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448545" name="Rectangle 4">
+        <xdr:cNvPr id="448551" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9B4619D-4E7C-8901-3551-8339150D3030}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF5E329C-84D7-220E-4B6F-558B875BC3DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1266,10 +1290,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448546" name="Text Box 5">
+        <xdr:cNvPr id="448552" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B5E4C2C-E159-CA56-AF89-CEF9FBF3277D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC774DEE-1ED3-F944-BCE8-2BDE0E92061C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1330,7 +1354,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9188E755-44AF-0AD3-83DC-D34BF40CC5EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0031773D-E6C4-50B1-CABD-AE17B1A59423}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,11 +1730,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790DBD09-F7D2-4B97-9332-740FFB20C498}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E55D92-73C7-458D-B7EE-C27D75658615}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="7.875" style="28" customWidth="1"/>
@@ -1731,21 +1755,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="57"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="21"/>
@@ -1797,20 +1821,20 @@
       <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="29" t="s">
@@ -1851,62 +1875,62 @@
       <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
     </row>
     <row r="15" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.6">
@@ -1943,10 +1967,10 @@
       <c r="K16" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="65" t="s">
+      <c r="L16" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="65"/>
+      <c r="M16" s="54"/>
     </row>
     <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="47"/>
@@ -1960,8 +1984,8 @@
       <c r="I17" s="37"/>
       <c r="J17" s="48"/>
       <c r="K17" s="47"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="52"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="75"/>
     </row>
     <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="47"/>
@@ -1975,8 +1999,8 @@
       <c r="I18" s="37"/>
       <c r="J18" s="48"/>
       <c r="K18" s="47"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="52"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="75"/>
     </row>
     <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="47"/>
@@ -1990,8 +2014,8 @@
       <c r="I19" s="37"/>
       <c r="J19" s="48"/>
       <c r="K19" s="47"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="52"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="75"/>
     </row>
     <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="47"/>
@@ -2005,8 +2029,8 @@
       <c r="I20" s="37"/>
       <c r="J20" s="48"/>
       <c r="K20" s="47"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="52"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="75"/>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="47"/>
@@ -2020,8 +2044,8 @@
       <c r="I21" s="37"/>
       <c r="J21" s="48"/>
       <c r="K21" s="47"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="75"/>
     </row>
     <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="47"/>
@@ -2035,8 +2059,8 @@
       <c r="I22" s="37"/>
       <c r="J22" s="48"/>
       <c r="K22" s="47"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="52"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="75"/>
     </row>
     <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="47"/>
@@ -2050,8 +2074,8 @@
       <c r="I23" s="37"/>
       <c r="J23" s="48"/>
       <c r="K23" s="47"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="52"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="47"/>
@@ -2065,8 +2089,8 @@
       <c r="I24" s="37"/>
       <c r="J24" s="48"/>
       <c r="K24" s="47"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="52"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="47"/>
@@ -2080,8 +2104,8 @@
       <c r="I25" s="37"/>
       <c r="J25" s="48"/>
       <c r="K25" s="47"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="52"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="47"/>
@@ -2095,8 +2119,8 @@
       <c r="I26" s="37"/>
       <c r="J26" s="48"/>
       <c r="K26" s="47"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="52"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="75"/>
     </row>
     <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="47"/>
@@ -2110,8 +2134,8 @@
       <c r="I27" s="37"/>
       <c r="J27" s="48"/>
       <c r="K27" s="47"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="52"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="75"/>
     </row>
     <row r="28" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="47"/>
@@ -2125,114 +2149,133 @@
       <c r="I28" s="37"/>
       <c r="J28" s="48"/>
       <c r="K28" s="47"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="52"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="75"/>
     </row>
     <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="55"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="64"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="47"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="59"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" s="68"/>
+    </row>
+    <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="57"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-    </row>
-    <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="63" t="s">
+      <c r="A32" s="66"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="K33" s="28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="H33" s="63" t="s">
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+    </row>
+    <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="H35" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="63"/>
-      <c r="J33" s="63"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="63"/>
-      <c r="M33" s="63"/>
-    </row>
-    <row r="34" spans="1:17" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="31"/>
-      <c r="B35" s="32" t="s">
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="72"/>
+    </row>
+    <row r="36" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
+    <row r="37" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
     </row>
     <row r="49" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D49" s="44"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="44"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="44"/>
-      <c r="L49" s="44"/>
-      <c r="M49" s="44"/>
-      <c r="N49" s="44"/>
-      <c r="O49" s="44"/>
-      <c r="P49" s="44"/>
-      <c r="Q49" s="44"/>
     </row>
     <row r="50" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D50" s="44"/>
@@ -2253,49 +2296,49 @@
     <row r="51" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D51" s="44"/>
       <c r="E51" s="44"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="45"/>
-      <c r="N51" s="45"/>
-      <c r="O51" s="45"/>
-      <c r="P51" s="45"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
       <c r="Q51" s="44"/>
     </row>
     <row r="52" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D52" s="44"/>
       <c r="E52" s="44"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+      <c r="P52" s="44"/>
       <c r="Q52" s="44"/>
     </row>
     <row r="53" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D53" s="44"/>
       <c r="E53" s="44"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
+      <c r="N53" s="45"/>
+      <c r="O53" s="45"/>
+      <c r="P53" s="45"/>
       <c r="Q53" s="44"/>
     </row>
     <row r="54" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
@@ -2925,21 +2968,71 @@
     <row r="93" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D93" s="44"/>
       <c r="E93" s="44"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="44"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="44"/>
-      <c r="L93" s="44"/>
-      <c r="M93" s="44"/>
-      <c r="N93" s="44"/>
-      <c r="O93" s="44"/>
-      <c r="P93" s="44"/>
+      <c r="F93" s="46"/>
+      <c r="G93" s="46"/>
+      <c r="H93" s="46"/>
+      <c r="I93" s="46"/>
+      <c r="J93" s="46"/>
+      <c r="K93" s="46"/>
+      <c r="L93" s="46"/>
+      <c r="M93" s="46"/>
+      <c r="N93" s="46"/>
+      <c r="O93" s="46"/>
+      <c r="P93" s="46"/>
       <c r="Q93" s="44"/>
     </row>
+    <row r="94" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="46"/>
+      <c r="H94" s="46"/>
+      <c r="I94" s="46"/>
+      <c r="J94" s="46"/>
+      <c r="K94" s="46"/>
+      <c r="L94" s="46"/>
+      <c r="M94" s="46"/>
+      <c r="N94" s="46"/>
+      <c r="O94" s="46"/>
+      <c r="P94" s="46"/>
+      <c r="Q94" s="44"/>
+    </row>
+    <row r="95" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="F95" s="44"/>
+      <c r="G95" s="44"/>
+      <c r="H95" s="44"/>
+      <c r="I95" s="44"/>
+      <c r="J95" s="44"/>
+      <c r="K95" s="44"/>
+      <c r="L95" s="44"/>
+      <c r="M95" s="44"/>
+      <c r="N95" s="44"/>
+      <c r="O95" s="44"/>
+      <c r="P95" s="44"/>
+      <c r="Q95" s="44"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="H32:M32"/>
     <mergeCell ref="C14:M14"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="A1:M1"/>
@@ -2947,25 +3040,6 @@
     <mergeCell ref="C11:M11"/>
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="C13:M13"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2977,7 +3051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7485F-3311-405B-9ABA-E42213A80AA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9624AA6D-A875-4628-838B-6C54C585AC13}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -2995,21 +3069,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="82"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4"/>
@@ -3024,10 +3098,10 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="82"/>
+      <c r="B3" s="83"/>
       <c r="C3" s="8" t="s">
         <v>25</v>
       </c>
@@ -3038,19 +3112,19 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="85"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="85"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
@@ -3063,23 +3137,23 @@
       <c r="B6" s="11"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="83" t="s">
+      <c r="B7" s="83"/>
+      <c r="C7" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="6" t="s">
@@ -3114,31 +3188,31 @@
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2" t="s">
@@ -3150,11 +3224,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="77">
+      <c r="H13" s="88">
         <v>38155</v>
       </c>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
@@ -3166,11 +3240,11 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="77">
+      <c r="H14" s="88">
         <v>38155</v>
       </c>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
@@ -3180,10 +3254,10 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="74"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
@@ -3208,17 +3282,17 @@
       <c r="K16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="75" t="s">
+      <c r="L16" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="76"/>
+      <c r="M16" s="87"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -3227,16 +3301,16 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <f t="shared" ref="A18:A31" si="0">A17+1</f>
         <v>2</v>
       </c>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -3245,16 +3319,16 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -3263,16 +3337,16 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -3281,16 +3355,16 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
+      <c r="L20" s="76"/>
+      <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -3299,16 +3373,16 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="74"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -3317,16 +3391,16 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -3335,16 +3409,16 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -3353,16 +3427,16 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -3371,16 +3445,16 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -3389,16 +3463,16 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -3407,16 +3481,16 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -3425,16 +3499,16 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -3443,16 +3517,16 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
+      <c r="L29" s="76"/>
+      <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -3461,16 +3535,16 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -3479,36 +3553,36 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="81"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="81"/>
+      <c r="A33" s="79"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="84" t="s">
+      <c r="A34" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="I34" s="84" t="s">
+      <c r="B34" s="78"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="I34" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="84"/>
-      <c r="M34" s="84"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="78"/>
+      <c r="M34" s="78"/>
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="15" t="s">
@@ -3532,6 +3606,42 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="L20:M20"/>
@@ -3542,42 +3652,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DC0858E-89F8-4C05-ADAC-17B0E5149A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2321992C-D9D6-4948-A42E-2C347A3FCE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{E9A8F0B2-F75E-4977-8CF6-0720706289C5}"/>
+    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{16B9C378-4408-4EB4-8365-1A320A24D0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
@@ -885,14 +885,14 @@
   <cellStyles count="10">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{717C8F23-486C-44C6-A90B-F8202DE11CF0}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{772D924A-BE3D-4807-A50A-F007D2BDA99B}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{F6F63994-74B6-43FB-8EFC-A8CB30903437}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{4A691EEE-C59C-45E9-B150-7163AA3658AF}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EB26CB89-3DBA-4939-87EC-B0F31E568BB6}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{28CBBCC1-F50D-4E20-948E-9ACCD4A6903B}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{A629EC5D-059A-4169-A445-ABEEB3C77DA7}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{04C086D6-7A37-4E43-A2ED-B89690D7DC37}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{86F2BF42-DBB4-4597-B7ED-1DAC6F181705}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{06DA4C54-8DAE-492A-A00F-C47EE1ED3371}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{733826C8-14B3-45D2-A90C-DBB6BE741562}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{E9EA3D9E-90AC-4E54-BEC3-02070A18A114}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{0F5203D5-DF5F-4052-93BE-9F35235972DF}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{E3CB279E-A254-4B71-A0D9-678F0EA4EE4A}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{67C58C37-96DA-40AC-A99E-EC20FD65AECB}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{01F27F39-7DDA-4917-A2D5-E5499E3B807E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -927,7 +927,7 @@
         <xdr:cNvPr id="447506" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{643A353F-BB83-BB5F-D019-B194ED2A58D0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A94F8CD-15DF-0FF3-B1AD-D22E1BAF7ADB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -976,7 +976,7 @@
         <xdr:cNvPr id="447507" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F67CD93-072F-D187-477B-F5A5759E7DC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E320A2E-E6A7-3C9B-5BD5-29581C9C5D66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1025,7 +1025,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F8A684B-37F2-7019-D4EC-38375DF32198}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEEB250D-7093-5B7A-E8BA-4CA5C28CA8D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1090,7 +1090,7 @@
         <xdr:cNvPr id="448548" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E8EDB46-27EF-9728-EFDF-156E315928DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A48DBF43-F19A-A5D3-0E79-F91F969E0837}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1139,7 +1139,7 @@
         <xdr:cNvPr id="448549" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0FB2B7-A5AF-EE88-CB6F-459251682708}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F2474D9-235B-0891-215D-E65D7A3E6D12}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1195,7 +1195,7 @@
         <xdr:cNvPr id="448550" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C690E942-0919-F250-DFF3-94C12BD57CC6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437EBABA-3A66-2EB7-8F8B-C745B4C509A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1244,7 +1244,7 @@
         <xdr:cNvPr id="448551" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF5E329C-84D7-220E-4B6F-558B875BC3DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD61265E-E7A8-C7C9-E452-043BAD6D5825}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1293,7 +1293,7 @@
         <xdr:cNvPr id="448552" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC774DEE-1ED3-F944-BCE8-2BDE0E92061C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A2D478B-4392-0323-491D-10DDD4602AFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1354,7 +1354,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0031773D-E6C4-50B1-CABD-AE17B1A59423}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5D2A27-F8F5-AAD9-A799-01812CBEDDB8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,7 +1730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E55D92-73C7-458D-B7EE-C27D75658615}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B06AA31-9B0C-4FF3-A62A-45958BB9A7D5}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3051,7 +3051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9624AA6D-A875-4628-838B-6C54C585AC13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BC93B2-F00C-498F-90FC-2EF9B26049D1}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2321992C-D9D6-4948-A42E-2C347A3FCE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDECAA84-3004-435A-B77A-D5350419731B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{16B9C378-4408-4EB4-8365-1A320A24D0CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5CF61F-83D5-4046-9300-35AE9610D147}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
     <sheet name="CHORE CFS" sheetId="7" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CHORE CY'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CHORE CY'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>GATE IN / GATE OUT REQUEST</t>
   </si>
@@ -177,24 +177,26 @@
     <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
   </si>
   <si>
-    <t>E-MAIL</t>
-  </si>
-  <si>
-    <t>CONTACT / TEL NO.</t>
-  </si>
-  <si>
     <t>CASH</t>
+  </si>
+  <si>
+    <t>NAME / ชื่อ :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL / โทร :   </t>
+  </si>
+  <si>
+    <t>EMAIL :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="214" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="218" formatCode="[$-1010000]d/m/yyyy\ h:mm\ &quot;น.&quot;;@"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -320,6 +322,12 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -382,13 +390,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Bookman Old Style"/>
@@ -400,6 +401,20 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -506,52 +521,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="dotted">
@@ -599,23 +568,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -707,19 +723,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -740,7 +750,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -749,22 +759,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="25" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,19 +783,67 @@
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -794,73 +852,37 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="218" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="214" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -869,30 +891,25 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="214" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="11">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{86F2BF42-DBB4-4597-B7ED-1DAC6F181705}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{06DA4C54-8DAE-492A-A00F-C47EE1ED3371}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{733826C8-14B3-45D2-A90C-DBB6BE741562}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{E9EA3D9E-90AC-4E54-BEC3-02070A18A114}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{0F5203D5-DF5F-4052-93BE-9F35235972DF}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{E3CB279E-A254-4B71-A0D9-678F0EA4EE4A}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{67C58C37-96DA-40AC-A99E-EC20FD65AECB}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="9" xr:uid="{01F27F39-7DDA-4917-A2D5-E5499E3B807E}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{947471E4-3DF6-457C-B904-0479D0184B5F}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{1542C173-D4F7-4DAD-BAEC-DD89577DA802}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{1CDC27BD-A92B-4689-B5EE-B7E96C44086A}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{F500C095-8E32-4FCE-B26A-33EAA9D2EEF4}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EF3988C9-AE00-41AC-88E5-79203A674FCF}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{46DC5825-762B-4F32-BD0E-CFA6FA1B5472}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{9EC789AA-C1AB-40E8-ABE7-3655E37A0C7D}"/>
+    <cellStyle name="Normal_CHORE" xfId="9" xr:uid="{465FAC9D-E0D6-4CC0-BBCE-03044E0D5F69}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="10" xr:uid="{F4035A28-4CDB-4461-943D-668E1C1E97C8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -924,10 +941,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447506" name="Rectangle 1">
+        <xdr:cNvPr id="447509" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A94F8CD-15DF-0FF3-B1AD-D22E1BAF7ADB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B94507AF-E407-0ECB-542C-F80462B13D53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -973,10 +990,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447507" name="Rectangle 4">
+        <xdr:cNvPr id="447510" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E320A2E-E6A7-3C9B-5BD5-29581C9C5D66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0933982-DC0B-F70F-4C44-25E89F487173}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1025,7 +1042,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEEB250D-7093-5B7A-E8BA-4CA5C28CA8D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B58480-19E3-D785-A2F0-0B512403557D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1087,10 +1104,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448548" name="Rectangle 1">
+        <xdr:cNvPr id="448554" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A48DBF43-F19A-A5D3-0E79-F91F969E0837}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2C02B5-A1EB-BCAF-17A0-FDF6291DCBB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1136,10 +1153,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448549" name="Rectangle 2">
+        <xdr:cNvPr id="448555" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F2474D9-235B-0891-215D-E65D7A3E6D12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC16605-1DFF-6B2E-2BC9-7D519C39D751}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1192,10 +1209,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448550" name="Rectangle 3">
+        <xdr:cNvPr id="448556" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437EBABA-3A66-2EB7-8F8B-C745B4C509A6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A54DED3-B971-4C6F-874B-2F4E1BDABB9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1241,10 +1258,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448551" name="Rectangle 4">
+        <xdr:cNvPr id="448557" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD61265E-E7A8-C7C9-E452-043BAD6D5825}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07F58E32-D2C4-0042-4134-DB154E0E2846}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1290,10 +1307,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448552" name="Text Box 5">
+        <xdr:cNvPr id="448558" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A2D478B-4392-0323-491D-10DDD4602AFB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E001D7-856E-911C-286E-1474142ED1AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1354,7 +1371,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5D2A27-F8F5-AAD9-A799-01812CBEDDB8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9011B34C-735B-E7B0-79CB-85D1BE109157}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,11 +1747,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B06AA31-9B0C-4FF3-A62A-45958BB9A7D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC962EB-3EA0-4084-BB2E-ED4D85028029}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="7.875" style="28" customWidth="1"/>
@@ -1755,21 +1772,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="57"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="21"/>
@@ -1783,7 +1800,7 @@
       <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
@@ -1818,23 +1835,23 @@
       <c r="A6" s="25"/>
     </row>
     <row r="7" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="29" t="s">
@@ -1844,29 +1861,29 @@
       <c r="D9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="H9" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34" t="s">
+      <c r="C10" s="32"/>
+      <c r="D10" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="H10" s="34" t="s">
+      <c r="E10" s="32"/>
+      <c r="H10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
       <c r="K10" s="28" t="s">
         <v>9</v>
       </c>
@@ -1875,411 +1892,519 @@
       <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="59"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="15" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="41" t="s">
+      <c r="I16" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="J16" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="42" t="s">
+      <c r="K16" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="54" t="s">
+      <c r="L16" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="54"/>
+      <c r="M16" s="70"/>
     </row>
     <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="47"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="75"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="60"/>
     </row>
     <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="47"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="75"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="60"/>
     </row>
     <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="47"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="75"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="60"/>
     </row>
     <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="47"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="75"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="60"/>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="47"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="75"/>
+      <c r="A21" s="45"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="60"/>
     </row>
     <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="47"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="75"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="60"/>
     </row>
     <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="47"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="75"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="60"/>
     </row>
     <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="47"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="75"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="60"/>
     </row>
     <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="47"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="75"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="60"/>
     </row>
     <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="47"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="75"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="60"/>
     </row>
     <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="47"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="75"/>
+      <c r="A27" s="45"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="60"/>
     </row>
     <row r="28" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="47"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="75"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="60"/>
     </row>
     <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="64"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="63"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="47"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="67" t="s">
+      <c r="A30" s="45"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="65"/>
+    </row>
+    <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="49"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="49"/>
+    </row>
+    <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+    </row>
+    <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="57"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+    </row>
+    <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="68"/>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="51"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="66"/>
-      <c r="B32" s="66"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-    </row>
-    <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="44"/>
-      <c r="B33" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="K33" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-    </row>
-    <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="H35" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="72"/>
-      <c r="M35" s="72"/>
-    </row>
-    <row r="36" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="31"/>
-      <c r="B36" s="32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+    </row>
+    <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="55"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+    </row>
+    <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+    </row>
+    <row r="43" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="42"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+    </row>
+    <row r="44" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+    </row>
+    <row r="45" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="42"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+    </row>
+    <row r="46" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="43"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="43"/>
+      <c r="P46" s="43"/>
+      <c r="Q46" s="42"/>
+    </row>
+    <row r="47" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="42"/>
+    </row>
+    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="42"/>
     </row>
     <row r="49" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D49" s="44"/>
-      <c r="E49" s="44"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="42"/>
     </row>
     <row r="50" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
       <c r="F50" s="44"/>
       <c r="G50" s="44"/>
       <c r="H50" s="44"/>
@@ -2291,11 +2416,11 @@
       <c r="N50" s="44"/>
       <c r="O50" s="44"/>
       <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
+      <c r="Q50" s="42"/>
     </row>
     <row r="51" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D51" s="44"/>
-      <c r="E51" s="44"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
       <c r="F51" s="44"/>
       <c r="G51" s="44"/>
       <c r="H51" s="44"/>
@@ -2307,11 +2432,11 @@
       <c r="N51" s="44"/>
       <c r="O51" s="44"/>
       <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
+      <c r="Q51" s="42"/>
     </row>
     <row r="52" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
       <c r="F52" s="44"/>
       <c r="G52" s="44"/>
       <c r="H52" s="44"/>
@@ -2323,701 +2448,594 @@
       <c r="N52" s="44"/>
       <c r="O52" s="44"/>
       <c r="P52" s="44"/>
-      <c r="Q52" s="44"/>
+      <c r="Q52" s="42"/>
     </row>
     <row r="53" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="45"/>
-      <c r="O53" s="45"/>
-      <c r="P53" s="45"/>
-      <c r="Q53" s="44"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="44"/>
+      <c r="M53" s="44"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+      <c r="P53" s="44"/>
+      <c r="Q53" s="42"/>
     </row>
     <row r="54" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="44"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="44"/>
+      <c r="N54" s="44"/>
+      <c r="O54" s="44"/>
+      <c r="P54" s="44"/>
+      <c r="Q54" s="42"/>
     </row>
     <row r="55" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="44"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="44"/>
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
+      <c r="P55" s="44"/>
+      <c r="Q55" s="42"/>
     </row>
     <row r="56" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="44"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
+      <c r="Q56" s="42"/>
     </row>
     <row r="57" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D57" s="44"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="44"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
+      <c r="M57" s="44"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="44"/>
+      <c r="P57" s="44"/>
+      <c r="Q57" s="42"/>
     </row>
     <row r="58" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
-      <c r="M58" s="46"/>
-      <c r="N58" s="46"/>
-      <c r="O58" s="46"/>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="44"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
+      <c r="M58" s="44"/>
+      <c r="N58" s="44"/>
+      <c r="O58" s="44"/>
+      <c r="P58" s="44"/>
+      <c r="Q58" s="42"/>
     </row>
     <row r="59" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
-      <c r="M59" s="46"/>
-      <c r="N59" s="46"/>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="44"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="44"/>
+      <c r="M59" s="44"/>
+      <c r="N59" s="44"/>
+      <c r="O59" s="44"/>
+      <c r="P59" s="44"/>
+      <c r="Q59" s="42"/>
     </row>
     <row r="60" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="44"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+      <c r="L60" s="44"/>
+      <c r="M60" s="44"/>
+      <c r="N60" s="44"/>
+      <c r="O60" s="44"/>
+      <c r="P60" s="44"/>
+      <c r="Q60" s="42"/>
     </row>
     <row r="61" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
-      <c r="M61" s="46"/>
-      <c r="N61" s="46"/>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="44"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+      <c r="L61" s="44"/>
+      <c r="M61" s="44"/>
+      <c r="N61" s="44"/>
+      <c r="O61" s="44"/>
+      <c r="P61" s="44"/>
+      <c r="Q61" s="42"/>
     </row>
     <row r="62" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="46"/>
-      <c r="M62" s="46"/>
-      <c r="N62" s="46"/>
-      <c r="O62" s="46"/>
-      <c r="P62" s="46"/>
-      <c r="Q62" s="44"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="44"/>
+      <c r="L62" s="44"/>
+      <c r="M62" s="44"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="44"/>
+      <c r="P62" s="44"/>
+      <c r="Q62" s="42"/>
     </row>
     <row r="63" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="46"/>
-      <c r="N63" s="46"/>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46"/>
-      <c r="Q63" s="44"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="44"/>
+      <c r="K63" s="44"/>
+      <c r="L63" s="44"/>
+      <c r="M63" s="44"/>
+      <c r="N63" s="44"/>
+      <c r="O63" s="44"/>
+      <c r="P63" s="44"/>
+      <c r="Q63" s="42"/>
     </row>
     <row r="64" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="46"/>
-      <c r="N64" s="46"/>
-      <c r="O64" s="46"/>
-      <c r="P64" s="46"/>
-      <c r="Q64" s="44"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44"/>
+      <c r="J64" s="44"/>
+      <c r="K64" s="44"/>
+      <c r="L64" s="44"/>
+      <c r="M64" s="44"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="P64" s="44"/>
+      <c r="Q64" s="42"/>
     </row>
     <row r="65" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-      <c r="L65" s="46"/>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="46"/>
-      <c r="Q65" s="44"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+      <c r="L65" s="44"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="P65" s="44"/>
+      <c r="Q65" s="42"/>
     </row>
     <row r="66" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
-      <c r="M66" s="46"/>
-      <c r="N66" s="46"/>
-      <c r="O66" s="46"/>
-      <c r="P66" s="46"/>
-      <c r="Q66" s="44"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="44"/>
+      <c r="L66" s="44"/>
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+      <c r="P66" s="44"/>
+      <c r="Q66" s="42"/>
     </row>
     <row r="67" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
-      <c r="M67" s="46"/>
-      <c r="N67" s="46"/>
-      <c r="O67" s="46"/>
-      <c r="P67" s="46"/>
-      <c r="Q67" s="44"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44"/>
+      <c r="J67" s="44"/>
+      <c r="K67" s="44"/>
+      <c r="L67" s="44"/>
+      <c r="M67" s="44"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="44"/>
+      <c r="P67" s="44"/>
+      <c r="Q67" s="42"/>
     </row>
     <row r="68" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-      <c r="L68" s="46"/>
-      <c r="M68" s="46"/>
-      <c r="N68" s="46"/>
-      <c r="O68" s="46"/>
-      <c r="P68" s="46"/>
-      <c r="Q68" s="44"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="44"/>
+      <c r="J68" s="44"/>
+      <c r="K68" s="44"/>
+      <c r="L68" s="44"/>
+      <c r="M68" s="44"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+      <c r="P68" s="44"/>
+      <c r="Q68" s="42"/>
     </row>
     <row r="69" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
-      <c r="L69" s="46"/>
-      <c r="M69" s="46"/>
-      <c r="N69" s="46"/>
-      <c r="O69" s="46"/>
-      <c r="P69" s="46"/>
-      <c r="Q69" s="44"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="44"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="44"/>
+      <c r="J69" s="44"/>
+      <c r="K69" s="44"/>
+      <c r="L69" s="44"/>
+      <c r="M69" s="44"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="44"/>
+      <c r="P69" s="44"/>
+      <c r="Q69" s="42"/>
     </row>
     <row r="70" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="46"/>
-      <c r="O70" s="46"/>
-      <c r="P70" s="46"/>
-      <c r="Q70" s="44"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="44"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="44"/>
+      <c r="L70" s="44"/>
+      <c r="M70" s="44"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="44"/>
+      <c r="P70" s="44"/>
+      <c r="Q70" s="42"/>
     </row>
     <row r="71" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
-      <c r="M71" s="46"/>
-      <c r="N71" s="46"/>
-      <c r="O71" s="46"/>
-      <c r="P71" s="46"/>
-      <c r="Q71" s="44"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="44"/>
+      <c r="J71" s="44"/>
+      <c r="K71" s="44"/>
+      <c r="L71" s="44"/>
+      <c r="M71" s="44"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="P71" s="44"/>
+      <c r="Q71" s="42"/>
     </row>
     <row r="72" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="46"/>
-      <c r="N72" s="46"/>
-      <c r="O72" s="46"/>
-      <c r="P72" s="46"/>
-      <c r="Q72" s="44"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="44"/>
+      <c r="L72" s="44"/>
+      <c r="M72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="P72" s="44"/>
+      <c r="Q72" s="42"/>
     </row>
     <row r="73" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D73" s="44"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
-      <c r="L73" s="46"/>
-      <c r="M73" s="46"/>
-      <c r="N73" s="46"/>
-      <c r="O73" s="46"/>
-      <c r="P73" s="46"/>
-      <c r="Q73" s="44"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="44"/>
+      <c r="I73" s="44"/>
+      <c r="J73" s="44"/>
+      <c r="K73" s="44"/>
+      <c r="L73" s="44"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="42"/>
     </row>
     <row r="74" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D74" s="44"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-      <c r="L74" s="46"/>
-      <c r="M74" s="46"/>
-      <c r="N74" s="46"/>
-      <c r="O74" s="46"/>
-      <c r="P74" s="46"/>
-      <c r="Q74" s="44"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="44"/>
+      <c r="I74" s="44"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="44"/>
+      <c r="L74" s="44"/>
+      <c r="M74" s="44"/>
+      <c r="N74" s="44"/>
+      <c r="O74" s="44"/>
+      <c r="P74" s="44"/>
+      <c r="Q74" s="42"/>
     </row>
     <row r="75" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D75" s="44"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
-      <c r="M75" s="46"/>
-      <c r="N75" s="46"/>
-      <c r="O75" s="46"/>
-      <c r="P75" s="46"/>
-      <c r="Q75" s="44"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
+      <c r="H75" s="44"/>
+      <c r="I75" s="44"/>
+      <c r="J75" s="44"/>
+      <c r="K75" s="44"/>
+      <c r="L75" s="44"/>
+      <c r="M75" s="44"/>
+      <c r="N75" s="44"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="42"/>
     </row>
     <row r="76" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D76" s="44"/>
-      <c r="E76" s="44"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="46"/>
-      <c r="M76" s="46"/>
-      <c r="N76" s="46"/>
-      <c r="O76" s="46"/>
-      <c r="P76" s="46"/>
-      <c r="Q76" s="44"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="44"/>
+      <c r="L76" s="44"/>
+      <c r="M76" s="44"/>
+      <c r="N76" s="44"/>
+      <c r="O76" s="44"/>
+      <c r="P76" s="44"/>
+      <c r="Q76" s="42"/>
     </row>
     <row r="77" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D77" s="44"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
-      <c r="L77" s="46"/>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="44"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
+      <c r="L77" s="44"/>
+      <c r="M77" s="44"/>
+      <c r="N77" s="44"/>
+      <c r="O77" s="44"/>
+      <c r="P77" s="44"/>
+      <c r="Q77" s="42"/>
     </row>
     <row r="78" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D78" s="44"/>
-      <c r="E78" s="44"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
-      <c r="M78" s="46"/>
-      <c r="N78" s="46"/>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="44"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44"/>
+      <c r="H78" s="44"/>
+      <c r="I78" s="44"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="44"/>
+      <c r="L78" s="44"/>
+      <c r="M78" s="44"/>
+      <c r="N78" s="44"/>
+      <c r="O78" s="44"/>
+      <c r="P78" s="44"/>
+      <c r="Q78" s="42"/>
     </row>
     <row r="79" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D79" s="44"/>
-      <c r="E79" s="44"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-      <c r="M79" s="46"/>
-      <c r="N79" s="46"/>
-      <c r="O79" s="46"/>
-      <c r="P79" s="46"/>
-      <c r="Q79" s="44"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+      <c r="L79" s="44"/>
+      <c r="M79" s="44"/>
+      <c r="N79" s="44"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="42"/>
     </row>
     <row r="80" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D80" s="44"/>
-      <c r="E80" s="44"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
-      <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
-      <c r="O80" s="46"/>
-      <c r="P80" s="46"/>
-      <c r="Q80" s="44"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="44"/>
+      <c r="I80" s="44"/>
+      <c r="J80" s="44"/>
+      <c r="K80" s="44"/>
+      <c r="L80" s="44"/>
+      <c r="M80" s="44"/>
+      <c r="N80" s="44"/>
+      <c r="O80" s="44"/>
+      <c r="P80" s="44"/>
+      <c r="Q80" s="42"/>
     </row>
     <row r="81" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D81" s="44"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="46"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
-      <c r="L81" s="46"/>
-      <c r="M81" s="46"/>
-      <c r="N81" s="46"/>
-      <c r="O81" s="46"/>
-      <c r="P81" s="46"/>
-      <c r="Q81" s="44"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
+      <c r="I81" s="44"/>
+      <c r="J81" s="44"/>
+      <c r="K81" s="44"/>
+      <c r="L81" s="44"/>
+      <c r="M81" s="44"/>
+      <c r="N81" s="44"/>
+      <c r="O81" s="44"/>
+      <c r="P81" s="44"/>
+      <c r="Q81" s="42"/>
     </row>
     <row r="82" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D82" s="44"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="46"/>
-      <c r="M82" s="46"/>
-      <c r="N82" s="46"/>
-      <c r="O82" s="46"/>
-      <c r="P82" s="46"/>
-      <c r="Q82" s="44"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="44"/>
+      <c r="I82" s="44"/>
+      <c r="J82" s="44"/>
+      <c r="K82" s="44"/>
+      <c r="L82" s="44"/>
+      <c r="M82" s="44"/>
+      <c r="N82" s="44"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="42"/>
     </row>
     <row r="83" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D83" s="44"/>
-      <c r="E83" s="44"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
-      <c r="N83" s="46"/>
-      <c r="O83" s="46"/>
-      <c r="P83" s="46"/>
-      <c r="Q83" s="44"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="44"/>
+      <c r="J83" s="44"/>
+      <c r="K83" s="44"/>
+      <c r="L83" s="44"/>
+      <c r="M83" s="44"/>
+      <c r="N83" s="44"/>
+      <c r="O83" s="44"/>
+      <c r="P83" s="44"/>
+      <c r="Q83" s="42"/>
     </row>
     <row r="84" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D84" s="44"/>
-      <c r="E84" s="44"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-      <c r="L84" s="46"/>
-      <c r="M84" s="46"/>
-      <c r="N84" s="46"/>
-      <c r="O84" s="46"/>
-      <c r="P84" s="46"/>
-      <c r="Q84" s="44"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+      <c r="L84" s="44"/>
+      <c r="M84" s="44"/>
+      <c r="N84" s="44"/>
+      <c r="O84" s="44"/>
+      <c r="P84" s="44"/>
+      <c r="Q84" s="42"/>
     </row>
     <row r="85" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D85" s="44"/>
-      <c r="E85" s="44"/>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="46"/>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-      <c r="L85" s="46"/>
-      <c r="M85" s="46"/>
-      <c r="N85" s="46"/>
-      <c r="O85" s="46"/>
-      <c r="P85" s="46"/>
-      <c r="Q85" s="44"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
+      <c r="I85" s="44"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
+      <c r="L85" s="44"/>
+      <c r="M85" s="44"/>
+      <c r="N85" s="44"/>
+      <c r="O85" s="44"/>
+      <c r="P85" s="44"/>
+      <c r="Q85" s="42"/>
     </row>
     <row r="86" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D86" s="44"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-      <c r="L86" s="46"/>
-      <c r="M86" s="46"/>
-      <c r="N86" s="46"/>
-      <c r="O86" s="46"/>
-      <c r="P86" s="46"/>
-      <c r="Q86" s="44"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
+      <c r="K86" s="44"/>
+      <c r="L86" s="44"/>
+      <c r="M86" s="44"/>
+      <c r="N86" s="44"/>
+      <c r="O86" s="44"/>
+      <c r="P86" s="44"/>
+      <c r="Q86" s="42"/>
     </row>
     <row r="87" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D87" s="44"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
-      <c r="P87" s="46"/>
-      <c r="Q87" s="44"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="44"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="44"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="44"/>
+      <c r="L87" s="44"/>
+      <c r="M87" s="44"/>
+      <c r="N87" s="44"/>
+      <c r="O87" s="44"/>
+      <c r="P87" s="44"/>
+      <c r="Q87" s="42"/>
     </row>
     <row r="88" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D88" s="44"/>
-      <c r="E88" s="44"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
-      <c r="M88" s="46"/>
-      <c r="N88" s="46"/>
-      <c r="O88" s="46"/>
-      <c r="P88" s="46"/>
-      <c r="Q88" s="44"/>
-    </row>
-    <row r="89" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D89" s="44"/>
-      <c r="E89" s="44"/>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46"/>
-      <c r="I89" s="46"/>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
-      <c r="L89" s="46"/>
-      <c r="M89" s="46"/>
-      <c r="N89" s="46"/>
-      <c r="O89" s="46"/>
-      <c r="P89" s="46"/>
-      <c r="Q89" s="44"/>
-    </row>
-    <row r="90" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D90" s="44"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="46"/>
-      <c r="M90" s="46"/>
-      <c r="N90" s="46"/>
-      <c r="O90" s="46"/>
-      <c r="P90" s="46"/>
-      <c r="Q90" s="44"/>
-    </row>
-    <row r="91" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D91" s="44"/>
-      <c r="E91" s="44"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-      <c r="L91" s="46"/>
-      <c r="M91" s="46"/>
-      <c r="N91" s="46"/>
-      <c r="O91" s="46"/>
-      <c r="P91" s="46"/>
-      <c r="Q91" s="44"/>
-    </row>
-    <row r="92" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D92" s="44"/>
-      <c r="E92" s="44"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="46"/>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-      <c r="L92" s="46"/>
-      <c r="M92" s="46"/>
-      <c r="N92" s="46"/>
-      <c r="O92" s="46"/>
-      <c r="P92" s="46"/>
-      <c r="Q92" s="44"/>
-    </row>
-    <row r="93" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D93" s="44"/>
-      <c r="E93" s="44"/>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="46"/>
-      <c r="I93" s="46"/>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-      <c r="L93" s="46"/>
-      <c r="M93" s="46"/>
-      <c r="N93" s="46"/>
-      <c r="O93" s="46"/>
-      <c r="P93" s="46"/>
-      <c r="Q93" s="44"/>
-    </row>
-    <row r="94" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="D94" s="44"/>
-      <c r="E94" s="44"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
-      <c r="H94" s="46"/>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
-      <c r="M94" s="46"/>
-      <c r="N94" s="46"/>
-      <c r="O94" s="46"/>
-      <c r="P94" s="46"/>
-      <c r="Q94" s="44"/>
-    </row>
-    <row r="95" spans="4:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="F95" s="44"/>
-      <c r="G95" s="44"/>
-      <c r="H95" s="44"/>
-      <c r="I95" s="44"/>
-      <c r="J95" s="44"/>
-      <c r="K95" s="44"/>
-      <c r="L95" s="44"/>
-      <c r="M95" s="44"/>
-      <c r="N95" s="44"/>
-      <c r="O95" s="44"/>
-      <c r="P95" s="44"/>
-      <c r="Q95" s="44"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="42"/>
+      <c r="L88" s="42"/>
+      <c r="M88" s="42"/>
+      <c r="N88" s="42"/>
+      <c r="O88" s="42"/>
+      <c r="P88" s="42"/>
+      <c r="Q88" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="C11:M11"/>
+    <mergeCell ref="C12:M12"/>
+    <mergeCell ref="C13:M13"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="L18:M18"/>
@@ -3025,21 +3043,16 @@
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="C11:M11"/>
-    <mergeCell ref="C12:M12"/>
-    <mergeCell ref="C13:M13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C32:M32"/>
+    <mergeCell ref="C33:M33"/>
+    <mergeCell ref="C34:M34"/>
+    <mergeCell ref="C35:M35"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3051,7 +3064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BC93B2-F00C-498F-90FC-2EF9B26049D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FE0FF24-5B80-4589-85C2-4858A2A6AE9F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -3069,21 +3082,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="82"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4"/>
@@ -3098,10 +3111,10 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="83"/>
+      <c r="B3" s="87"/>
       <c r="C3" s="8" t="s">
         <v>25</v>
       </c>
@@ -3112,19 +3125,19 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="77"/>
+      <c r="B4" s="90"/>
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="77"/>
+      <c r="B5" s="90"/>
       <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
@@ -3137,23 +3150,23 @@
       <c r="B6" s="11"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="84" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="6" t="s">
@@ -3188,31 +3201,31 @@
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2" t="s">
@@ -3224,11 +3237,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="88">
+      <c r="H13" s="82">
         <v>38155</v>
       </c>
-      <c r="I13" s="88"/>
-      <c r="J13" s="88"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
@@ -3240,11 +3253,11 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="88">
+      <c r="H14" s="82">
         <v>38155</v>
       </c>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
@@ -3254,10 +3267,10 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="76"/>
+      <c r="C16" s="79"/>
       <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
@@ -3282,17 +3295,17 @@
       <c r="K16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="86" t="s">
+      <c r="L16" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="87"/>
+      <c r="M16" s="81"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -3301,16 +3314,16 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <f t="shared" ref="A18:A31" si="0">A17+1</f>
         <v>2</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -3319,16 +3332,16 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -3337,16 +3350,16 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -3355,16 +3368,16 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B21" s="76"/>
-      <c r="C21" s="76"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -3373,16 +3386,16 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -3391,16 +3404,16 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -3409,16 +3422,16 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="79"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -3427,16 +3440,16 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -3445,16 +3458,16 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -3463,16 +3476,16 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="76"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -3481,16 +3494,16 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -3499,16 +3512,16 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -3517,16 +3530,16 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="76"/>
-      <c r="M29" s="76"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -3535,16 +3548,16 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -3553,36 +3566,36 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="79"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
+      <c r="A33" s="86"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="I34" s="78" t="s">
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="I34" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="78"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
+      <c r="M34" s="89"/>
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="15" t="s">
@@ -3606,22 +3619,26 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A3:B3"/>
@@ -3632,26 +3649,22 @@
     <mergeCell ref="L24:M24"/>
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L21:M21"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/templates/B3-SHORE.xlsx
+++ b/docs/templates/B3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDECAA84-3004-435A-B77A-D5350419731B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B78B92C-F982-4AC1-91CF-4543E4D37DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5CF61F-83D5-4046-9300-35AE9610D147}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2165F01-7CA3-4E27-A17E-E5E71FBC3CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="CHORE CY" sheetId="8" r:id="rId1"/>
@@ -397,10 +397,10 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -411,10 +411,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -521,6 +521,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="dotted">
@@ -568,52 +614,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -783,16 +783,73 @@
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
@@ -801,115 +858,58 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="214" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="214" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{947471E4-3DF6-457C-B904-0479D0184B5F}"/>
-    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{1542C173-D4F7-4DAD-BAEC-DD89577DA802}"/>
-    <cellStyle name="Normal 14" xfId="4" xr:uid="{1CDC27BD-A92B-4689-B5EE-B7E96C44086A}"/>
-    <cellStyle name="Normal 2" xfId="5" xr:uid="{F500C095-8E32-4FCE-B26A-33EAA9D2EEF4}"/>
-    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{EF3988C9-AE00-41AC-88E5-79203A674FCF}"/>
-    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{46DC5825-762B-4F32-BD0E-CFA6FA1B5472}"/>
-    <cellStyle name="Normal 4" xfId="8" xr:uid="{9EC789AA-C1AB-40E8-ABE7-3655E37A0C7D}"/>
-    <cellStyle name="Normal_CHORE" xfId="9" xr:uid="{465FAC9D-E0D6-4CC0-BBCE-03044E0D5F69}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="10" xr:uid="{F4035A28-4CDB-4461-943D-668E1C1E97C8}"/>
+    <cellStyle name="Normal 10 10" xfId="2" xr:uid="{8ECE1D79-DE0D-407C-9AC0-DF10293F6B55}"/>
+    <cellStyle name="Normal 10 2 10" xfId="3" xr:uid="{48639F6E-BC2D-4C77-86C6-E713A05D3356}"/>
+    <cellStyle name="Normal 14" xfId="4" xr:uid="{44415769-CB04-4D32-905B-96EA596B5224}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{B52F1BE5-B73A-4485-A36C-B871C8E0903B}"/>
+    <cellStyle name="Normal 2 10" xfId="6" xr:uid="{7D482B9D-D4B9-461C-95FF-543CAE0D972D}"/>
+    <cellStyle name="Normal 2 2 2" xfId="7" xr:uid="{0EB9EB15-0757-495B-B755-11868B4FAA9F}"/>
+    <cellStyle name="Normal 4" xfId="8" xr:uid="{BAC3AC65-27DA-4E44-9C6E-358F9E2A4E5A}"/>
+    <cellStyle name="Normal_CHORE" xfId="9" xr:uid="{415BA214-1BB4-4098-9AED-9A42C5D5515B}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="10" xr:uid="{E2768AC4-54A5-4D3F-BBFD-93C23B03DE08}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -941,10 +941,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447509" name="Rectangle 1">
+        <xdr:cNvPr id="447512" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B94507AF-E407-0ECB-542C-F80462B13D53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923227A0-B476-4B23-5A0B-54CCE66A6DA5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -954,8 +954,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6362700" y="2194560"/>
-          <a:ext cx="899160" cy="205740"/>
+          <a:off x="7139940" y="2194560"/>
+          <a:ext cx="1386840" cy="205740"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -990,10 +990,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="447510" name="Rectangle 4">
+        <xdr:cNvPr id="447513" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0933982-DC0B-F70F-4C44-25E89F487173}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD020765-D5B5-EF7F-A9C3-F4280A15317E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1042,7 +1042,7 @@
         <xdr:cNvPr id="390163" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B58480-19E3-D785-A2F0-0B512403557D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C643476-0ED0-D3B4-3ABF-C00758EBB555}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1104,10 +1104,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448554" name="Rectangle 1">
+        <xdr:cNvPr id="448560" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2C02B5-A1EB-BCAF-17A0-FDF6291DCBB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42990F3B-3A57-9B97-A79A-AC20917C0CC2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1153,10 +1153,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448555" name="Rectangle 2">
+        <xdr:cNvPr id="448561" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC16605-1DFF-6B2E-2BC9-7D519C39D751}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3913132-3684-A1AF-6279-4D3335BC45DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1209,10 +1209,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448556" name="Rectangle 3">
+        <xdr:cNvPr id="448562" name="Rectangle 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A54DED3-B971-4C6F-874B-2F4E1BDABB9E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D35B0D5-237E-C241-079C-A722C38BB143}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1258,10 +1258,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448557" name="Rectangle 4">
+        <xdr:cNvPr id="448563" name="Rectangle 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07F58E32-D2C4-0042-4134-DB154E0E2846}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81F8FED6-7239-DA44-64AB-7777FAF3DBC1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1307,10 +1307,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="448558" name="Text Box 5">
+        <xdr:cNvPr id="448564" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E001D7-856E-911C-286E-1474142ED1AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE791002-28B9-6D0F-F3C2-F1305BF18270}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1371,7 @@
         <xdr:cNvPr id="12295" name="WordArt 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9011B34C-735B-E7B0-79CB-85D1BE109157}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373A9DEC-2F4D-7FB2-F68A-C1731BA3C103}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1747,7 +1747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC962EB-3EA0-4084-BB2E-ED4D85028029}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F71EF7-F013-46D6-ACD9-693703FA9C8D}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1761,9 +1761,9 @@
     <col min="5" max="5" width="9.75" style="28" customWidth="1"/>
     <col min="6" max="6" width="7.75" style="28" customWidth="1"/>
     <col min="7" max="7" width="20.875" style="28" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="28" customWidth="1"/>
-    <col min="9" max="9" width="6.25" style="28" customWidth="1"/>
-    <col min="10" max="10" width="24" style="28" customWidth="1"/>
+    <col min="8" max="8" width="12.125" style="28" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="28" customWidth="1"/>
+    <col min="10" max="10" width="32" style="28" customWidth="1"/>
     <col min="11" max="11" width="8" style="28" customWidth="1"/>
     <col min="12" max="12" width="7.875" style="28" customWidth="1"/>
     <col min="13" max="13" width="36.375" style="28" customWidth="1"/>
@@ -1772,21 +1772,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="21"/>
@@ -1838,20 +1838,20 @@
       <c r="A7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="29" t="s">
@@ -1892,62 +1892,62 @@
       <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
     </row>
     <row r="15" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.6"/>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.6">
@@ -1984,10 +1984,10 @@
       <c r="K16" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="70" t="s">
+      <c r="L16" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="70"/>
+      <c r="M16" s="65"/>
     </row>
     <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="45"/>
@@ -2001,8 +2001,8 @@
       <c r="I17" s="35"/>
       <c r="J17" s="46"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="60"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="74"/>
     </row>
     <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="45"/>
@@ -2016,8 +2016,8 @@
       <c r="I18" s="35"/>
       <c r="J18" s="46"/>
       <c r="K18" s="45"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="60"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="74"/>
     </row>
     <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="45"/>
@@ -2031,8 +2031,8 @@
       <c r="I19" s="35"/>
       <c r="J19" s="46"/>
       <c r="K19" s="45"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="60"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="74"/>
     </row>
     <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="45"/>
@@ -2046,8 +2046,8 @@
       <c r="I20" s="35"/>
       <c r="J20" s="46"/>
       <c r="K20" s="45"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="60"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="74"/>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="45"/>
@@ -2061,8 +2061,8 @@
       <c r="I21" s="35"/>
       <c r="J21" s="46"/>
       <c r="K21" s="45"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="60"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="45"/>
@@ -2076,8 +2076,8 @@
       <c r="I22" s="35"/>
       <c r="J22" s="46"/>
       <c r="K22" s="45"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="45"/>
@@ -2091,8 +2091,8 @@
       <c r="I23" s="35"/>
       <c r="J23" s="46"/>
       <c r="K23" s="45"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="60"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="74"/>
     </row>
     <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="45"/>
@@ -2106,8 +2106,8 @@
       <c r="I24" s="35"/>
       <c r="J24" s="46"/>
       <c r="K24" s="45"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="60"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="74"/>
     </row>
     <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="45"/>
@@ -2121,8 +2121,8 @@
       <c r="I25" s="35"/>
       <c r="J25" s="46"/>
       <c r="K25" s="45"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="74"/>
     </row>
     <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="45"/>
@@ -2136,8 +2136,8 @@
       <c r="I26" s="35"/>
       <c r="J26" s="46"/>
       <c r="K26" s="45"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="60"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="74"/>
     </row>
     <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="45"/>
@@ -2151,8 +2151,8 @@
       <c r="I27" s="35"/>
       <c r="J27" s="46"/>
       <c r="K27" s="45"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="74"/>
     </row>
     <row r="28" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="45"/>
@@ -2166,42 +2166,42 @@
       <c r="I28" s="35"/>
       <c r="J28" s="46"/>
       <c r="K28" s="45"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="60"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="74"/>
     </row>
     <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="62"/>
-      <c r="M29" s="63"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="58"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="45"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="64" t="s">
+      <c r="B30" s="61"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="M30" s="65"/>
+      <c r="M30" s="60"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="49"/>
@@ -2223,68 +2223,68 @@
         <v>19</v>
       </c>
       <c r="B32"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+      <c r="M32" s="77"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
     </row>
     <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="53"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
     </row>
     <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="54" t="s">
         <v>45</v>
       </c>
       <c r="B35" s="55"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="77"/>
+      <c r="M35" s="77"/>
     </row>
     <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="D42" s="42"/>
@@ -3026,6 +3026,23 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C32:M32"/>
+    <mergeCell ref="C33:M33"/>
+    <mergeCell ref="C34:M34"/>
+    <mergeCell ref="C35:M35"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="L30:M30"/>
     <mergeCell ref="B30:K30"/>
@@ -3036,23 +3053,6 @@
     <mergeCell ref="C11:M11"/>
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="C13:M13"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C32:M32"/>
-    <mergeCell ref="C33:M33"/>
-    <mergeCell ref="C34:M34"/>
-    <mergeCell ref="C35:M35"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3064,7 +3064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FE0FF24-5B80-4589-85C2-4858A2A6AE9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B65E605-1A93-4263-97C7-1C6C28C432FE}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -3082,21 +3082,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="85"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="84"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4"/>
@@ -3111,10 +3111,10 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="87"/>
+      <c r="B3" s="85"/>
       <c r="C3" s="8" t="s">
         <v>25</v>
       </c>
@@ -3125,19 +3125,19 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="90"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="90"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
@@ -3150,23 +3150,23 @@
       <c r="B6" s="11"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="88" t="s">
+      <c r="B7" s="85"/>
+      <c r="C7" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
+      <c r="M7" s="86"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="6" t="s">
@@ -3201,31 +3201,31 @@
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="78"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="87"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="78"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="87"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2" t="s">
@@ -3237,11 +3237,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="82">
+      <c r="H13" s="90">
         <v>38155</v>
       </c>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
@@ -3253,11 +3253,11 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="82">
+      <c r="H14" s="90">
         <v>38155</v>
       </c>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
@@ -3267,10 +3267,10 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="79"/>
+      <c r="C16" s="78"/>
       <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
@@ -3295,17 +3295,17 @@
       <c r="K16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="80" t="s">
+      <c r="L16" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="81"/>
+      <c r="M16" s="89"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -3314,16 +3314,16 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <f t="shared" ref="A18:A31" si="0">A17+1</f>
         <v>2</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -3332,16 +3332,16 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -3350,16 +3350,16 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -3368,16 +3368,16 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -3386,16 +3386,16 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -3404,16 +3404,16 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="79"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="78"/>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -3422,16 +3422,16 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="79"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -3440,16 +3440,16 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="78"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -3458,16 +3458,16 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
+      <c r="L25" s="78"/>
+      <c r="M25" s="78"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="78"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -3476,16 +3476,16 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="79"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="78"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -3494,16 +3494,16 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="78"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -3512,16 +3512,16 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
+      <c r="L28" s="78"/>
+      <c r="M28" s="78"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -3530,16 +3530,16 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
+      <c r="L29" s="78"/>
+      <c r="M29" s="78"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="78"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -3548,16 +3548,16 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
+      <c r="L30" s="78"/>
+      <c r="M30" s="78"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="78"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -3566,36 +3566,36 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="78"/>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="86"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="89" t="s">
+      <c r="A34" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="I34" s="89" t="s">
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="I34" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="89"/>
-      <c r="M34" s="89"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="15" t="s">
@@ -3619,6 +3619,42 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="L20:M20"/>
@@ -3629,42 +3665,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
